--- a/design/MiniTemplate/Excels/#role.xlsx
+++ b/design/MiniTemplate/Excels/#role.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BiliBili\Work\slime\design\MiniTemplate\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FB62DA-9D2E-4758-9882-9CE3670BC80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3997A019-F9BC-4CF3-8C91-FF86CC4400AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6552" yWindow="2100" windowWidth="20952" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="325">
   <si>
     <t>##var</t>
   </si>
@@ -115,17 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>role.Quality</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>role.Relation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>skills</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -607,15 +596,6 @@
     <t>孙悟空</t>
   </si>
   <si>
-    <t>LING</t>
-  </si>
-  <si>
-    <t>XIAN</t>
-  </si>
-  <si>
-    <t>SHEN</t>
-  </si>
-  <si>
     <t>#修正</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1035,6 +1015,34 @@
   </si>
   <si>
     <t>fensheng</t>
+  </si>
+  <si>
+    <t>RoleQuality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleRelation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>ling</t>
+  </si>
+  <si>
+    <t>xian</t>
+  </si>
+  <si>
+    <t>shen</t>
+  </si>
+  <si>
+    <t>xiangrui3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zuie2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1209,6 +1217,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1225,12 +1239,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1930,7 +1938,9 @@
   <cols>
     <col min="1" max="4" width="9.109375" style="1"/>
     <col min="5" max="5" width="14.77734375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="6" max="36" width="9.109375" style="1"/>
+    <col min="37" max="37" width="14.77734375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1953,83 +1963,83 @@
         <v>24</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="V1" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-      <c r="AI1" s="10"/>
-      <c r="AK1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AL1" s="9"/>
-      <c r="AM1" s="9"/>
-      <c r="AN1" s="9"/>
-      <c r="AO1" s="9"/>
-      <c r="AP1" s="9"/>
-      <c r="AQ1" s="9"/>
-      <c r="AR1" s="9"/>
-      <c r="AS1" s="10"/>
+        <v>187</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+      <c r="AI1" s="12"/>
+      <c r="AK1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL1" s="11"/>
+      <c r="AM1" s="11"/>
+      <c r="AN1" s="11"/>
+      <c r="AO1" s="11"/>
+      <c r="AP1" s="11"/>
+      <c r="AQ1" s="11"/>
+      <c r="AR1" s="11"/>
+      <c r="AS1" s="12"/>
     </row>
     <row r="2" spans="1:45" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2045,102 +2055,102 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>317</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y2" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y2" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="15"/>
+      <c r="AK2" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="13"/>
-      <c r="AK2" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL2" s="12"/>
-      <c r="AM2" s="12"/>
-      <c r="AN2" s="12"/>
-      <c r="AO2" s="12"/>
-      <c r="AP2" s="12"/>
-      <c r="AQ2" s="12"/>
-      <c r="AR2" s="12"/>
-      <c r="AS2" s="13"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="14"/>
+      <c r="AO2" s="14"/>
+      <c r="AP2" s="14"/>
+      <c r="AQ2" s="14"/>
+      <c r="AR2" s="14"/>
+      <c r="AS2" s="15"/>
     </row>
     <row r="3" spans="1:45" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="AB3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AC3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AD3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AE3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AF3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AD3" s="6" t="s">
+      <c r="AG3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AE3" s="6" t="s">
+      <c r="AH3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AI3" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="AG3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI3" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="AK3" s="5">
         <v>1</v>
@@ -2189,59 +2199,59 @@
       <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="R4" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="H4" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I4" s="15" t="s">
+      <c r="S4" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="V4" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q4" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="R4" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="S4" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="T4" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="U4" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="W4" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="X4" s="15" t="s">
-        <v>223</v>
+      <c r="W4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>10</v>
@@ -2279,7 +2289,7 @@
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>23</v>
@@ -2288,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(D5, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G5</f>
@@ -2392,21 +2402,21 @@
         <v>0</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(D6, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G6</f>
@@ -2510,21 +2520,21 @@
         <v>0</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(D7, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G7</f>
@@ -2628,21 +2638,21 @@
         <v>0</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(D8, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G8</f>
@@ -2746,21 +2756,21 @@
         <v>0</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(D9, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G9</f>
@@ -2864,21 +2874,21 @@
         <v>0</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(D10, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G10</f>
@@ -2982,24 +2992,24 @@
         <v>0</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1">
         <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(D11, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G11</f>
@@ -3103,24 +3113,24 @@
         <v>0</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1">
         <v>7</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(D12, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G12</f>
@@ -3224,24 +3234,24 @@
         <v>0.1</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(D13, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G13</f>
@@ -3345,24 +3355,24 @@
         <v>0.1</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1">
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(D14, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G14</f>
@@ -3466,24 +3476,24 @@
         <v>0.1</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1">
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(D15, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G15</f>
@@ -3587,24 +3597,24 @@
         <v>0.2</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1">
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(D16, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G16</f>
@@ -3708,24 +3718,24 @@
         <v>0.1</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(D17, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G17</f>
@@ -3829,21 +3839,21 @@
         <v>0</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(D18, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G18</f>
@@ -3947,21 +3957,21 @@
         <v>0</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(D19, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G19</f>
@@ -4065,21 +4075,21 @@
         <v>0</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(D20, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G20</f>
@@ -4183,24 +4193,24 @@
         <v>0.1</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(D21, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G21</f>
@@ -4304,24 +4314,24 @@
         <v>0</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1">
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(D22, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G22</f>
@@ -4425,24 +4435,24 @@
         <v>0</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AL22" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(D23, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G23</f>
@@ -4546,24 +4556,24 @@
         <v>0</v>
       </c>
       <c r="AK23" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="AL23" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="AL23" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="24" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(D24, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G24</f>
@@ -4667,21 +4677,21 @@
         <v>0</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(D25, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G25</f>
@@ -4785,24 +4795,24 @@
         <v>0</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D26" s="1">
         <v>6</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(D26, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G26</f>
@@ -4906,21 +4916,21 @@
         <v>0</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D27" s="1">
         <v>6</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(D27, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G27</f>
@@ -5024,24 +5034,24 @@
         <v>0</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D28" s="1">
         <v>7</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(D28, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G28</f>
@@ -5145,24 +5155,24 @@
         <v>0.1</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D29" s="1">
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(D29, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G29</f>
@@ -5266,24 +5276,24 @@
         <v>0.1</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AL29" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D30" s="1">
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(D30, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G30</f>
@@ -5387,24 +5397,24 @@
         <v>0.1</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AL30" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D31" s="1">
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(D31, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G31</f>
@@ -5508,24 +5518,24 @@
         <v>0.2</v>
       </c>
       <c r="AK31" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL31" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="AL31" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D32" s="1">
         <v>2</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(D32, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G32</f>
@@ -5629,21 +5639,21 @@
         <v>0</v>
       </c>
       <c r="AK32" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(D33, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G33</f>
@@ -5747,24 +5757,24 @@
         <v>0</v>
       </c>
       <c r="AK33" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AL33" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D34" s="1">
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(D34, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G34</f>
@@ -5868,24 +5878,24 @@
         <v>0</v>
       </c>
       <c r="AK34" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AL34" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" s="1">
         <v>5</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(D35, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G35</f>
@@ -5989,24 +5999,24 @@
         <v>0</v>
       </c>
       <c r="AK35" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AL35" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D36" s="1">
         <v>6</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(D36, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G36</f>
@@ -6110,24 +6120,24 @@
         <v>0</v>
       </c>
       <c r="AK36" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AL36" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D37" s="1">
         <v>7</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(D37, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G37</f>
@@ -6231,24 +6241,24 @@
         <v>0.2</v>
       </c>
       <c r="AK37" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AL37" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D38" s="1">
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(D38, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G38</f>
@@ -6352,24 +6362,24 @@
         <v>0.1</v>
       </c>
       <c r="AK38" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AL38" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D39" s="1">
         <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(D39, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G39</f>
@@ -6473,24 +6483,24 @@
         <v>0.2</v>
       </c>
       <c r="AK39" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AL39" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(D40, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G40</f>
@@ -6594,21 +6604,21 @@
         <v>0</v>
       </c>
       <c r="AK40" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(D41, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G41</f>
@@ -6712,21 +6722,21 @@
         <v>0</v>
       </c>
       <c r="AK41" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D42" s="1">
         <v>3</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(D42, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G42</f>
@@ -6830,21 +6840,21 @@
         <v>0</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D43" s="1">
         <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(D43, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G43</f>
@@ -6948,24 +6958,24 @@
         <v>0.05</v>
       </c>
       <c r="AK43" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AL43" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D44" s="1">
         <v>5</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(D44, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G44</f>
@@ -7069,24 +7079,24 @@
         <v>0.1</v>
       </c>
       <c r="AK44" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="AL44" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D45" s="1">
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(D45, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G45</f>
@@ -7190,24 +7200,24 @@
         <v>0.1</v>
       </c>
       <c r="AK45" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AL45" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D46" s="1">
         <v>7</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(D46, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G46</f>
@@ -7311,24 +7321,24 @@
         <v>0.1</v>
       </c>
       <c r="AK46" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AL46" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D47" s="1">
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(D47, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G47</f>
@@ -7432,24 +7442,24 @@
         <v>0.1</v>
       </c>
       <c r="AK47" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AL47" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D48" s="1">
         <v>9</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(D48, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G48</f>
@@ -7553,24 +7563,24 @@
         <v>0.1</v>
       </c>
       <c r="AK48" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AL48" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(D49, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G49</f>
@@ -7674,21 +7684,21 @@
         <v>0</v>
       </c>
       <c r="AK49" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D50" s="1">
         <v>3</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(D50, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G50</f>
@@ -7792,24 +7802,24 @@
         <v>0</v>
       </c>
       <c r="AK50" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AL50" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D51" s="1">
         <v>4</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(D51, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G51</f>
@@ -7913,24 +7923,24 @@
         <v>0</v>
       </c>
       <c r="AK51" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AL51" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B52" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D52" s="1">
         <v>5</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(D52, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G52</f>
@@ -8034,24 +8044,24 @@
         <v>0.2</v>
       </c>
       <c r="AK52" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AL52" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D53" s="1">
         <v>6</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(D53, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G53</f>
@@ -8155,21 +8165,21 @@
         <v>0.1</v>
       </c>
       <c r="AK53" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D54" s="1">
         <v>7</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(D54, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G54</f>
@@ -8273,24 +8283,24 @@
         <v>0.2</v>
       </c>
       <c r="AK54" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AL54" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B55" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D55" s="1">
         <v>8</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(D55, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G55</f>
@@ -8391,24 +8401,24 @@
         <v>0.2</v>
       </c>
       <c r="AK55" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AL55" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B56" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D56" s="1">
         <v>9</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(D56, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G56</f>
@@ -8512,24 +8522,24 @@
         <v>0.2</v>
       </c>
       <c r="AK56" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AL56" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="57" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B57" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(D57, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G57</f>
@@ -8633,24 +8643,24 @@
         <v>0</v>
       </c>
       <c r="AK57" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AL57" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B58" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D58" s="1">
         <v>5</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(D58, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G58</f>
@@ -8754,24 +8764,24 @@
         <v>0.1</v>
       </c>
       <c r="AK58" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AL58" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B59" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D59" s="1">
         <v>2</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(D59, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G59</f>
@@ -8875,21 +8885,21 @@
         <v>0</v>
       </c>
       <c r="AK59" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D60" s="1">
         <v>3</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(D60, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G60</f>
@@ -8993,24 +9003,24 @@
         <v>0</v>
       </c>
       <c r="AK60" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AL60" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B61" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(D61, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G61</f>
@@ -9114,24 +9124,24 @@
         <v>0</v>
       </c>
       <c r="AK61" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AL61" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B62" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D62" s="1">
         <v>5</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(D62, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G62</f>
@@ -9235,24 +9245,24 @@
         <v>0</v>
       </c>
       <c r="AK62" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AL62" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B63" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D63" s="1">
         <v>6</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(D63, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G63</f>
@@ -9356,24 +9366,24 @@
         <v>0.1</v>
       </c>
       <c r="AK63" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AL63" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B64" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D64" s="1">
         <v>7</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(D64, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G64</f>
@@ -9477,24 +9487,24 @@
         <v>0.1</v>
       </c>
       <c r="AK64" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AL64" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D65" s="1">
         <v>8</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(D65, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G65</f>
@@ -9598,24 +9608,24 @@
         <v>0.2</v>
       </c>
       <c r="AK65" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AL65" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D66" s="1">
         <v>3</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(D66, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G66</f>
@@ -9719,21 +9729,21 @@
         <v>0</v>
       </c>
       <c r="AK66" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="67" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B67" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(D67, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G67</f>
@@ -9837,24 +9847,24 @@
         <v>0</v>
       </c>
       <c r="AK67" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL67" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B68" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D68" s="1">
         <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(D68, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G68</f>
@@ -9958,24 +9968,24 @@
         <v>0.15</v>
       </c>
       <c r="AK68" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL68" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B69" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D69" s="1">
         <v>6</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(D69, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G69</f>
@@ -10079,24 +10089,24 @@
         <v>0.15</v>
       </c>
       <c r="AK69" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL69" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B70" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D70" s="1">
         <v>7</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(D70, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G70</f>
@@ -10200,24 +10210,24 @@
         <v>0.1</v>
       </c>
       <c r="AK70" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL70" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="71" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B71" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D71" s="1">
         <v>8</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(D71, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G71</f>
@@ -10321,24 +10331,24 @@
         <v>0.15</v>
       </c>
       <c r="AK71" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL71" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B72" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D72" s="1">
         <v>7</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(D72, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G72</f>
@@ -10442,24 +10452,24 @@
         <v>0.1</v>
       </c>
       <c r="AK72" s="1" t="s">
-        <v>241</v>
+        <v>323</v>
       </c>
       <c r="AL72" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B73" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D73" s="1">
         <v>8</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(D73, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G73</f>
@@ -10563,24 +10573,24 @@
         <v>0.1</v>
       </c>
       <c r="AK73" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AL73" s="1" t="s">
-        <v>258</v>
+        <v>324</v>
       </c>
     </row>
     <row r="74" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B74" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D74" s="1">
         <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(D74, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G74</f>
@@ -10684,24 +10694,24 @@
         <v>0.1</v>
       </c>
       <c r="AK74" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AL74" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B75" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D75" s="1">
         <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(D75, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G75</f>
@@ -10805,24 +10815,24 @@
         <v>0.1</v>
       </c>
       <c r="AK75" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AL75" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B76" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D76" s="1">
         <v>2</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(D76, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G76</f>
@@ -10926,24 +10936,24 @@
         <v>0.1</v>
       </c>
       <c r="AK76" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL76" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B77" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D77" s="1">
         <v>3</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(D77, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G77</f>
@@ -11047,21 +11057,21 @@
         <v>0.1</v>
       </c>
       <c r="AK77" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="78" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B78" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D78" s="1">
         <v>4</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(D78, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G78</f>
@@ -11165,24 +11175,24 @@
         <v>0.1</v>
       </c>
       <c r="AK78" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL78" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="79" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B79" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D79" s="1">
         <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(D79, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G79</f>
@@ -11286,24 +11296,24 @@
         <v>0.1</v>
       </c>
       <c r="AK79" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL79" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="80" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B80" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D80" s="1">
         <v>6</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(D80, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G80</f>
@@ -11407,24 +11417,24 @@
         <v>0.1</v>
       </c>
       <c r="AK80" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL80" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B81" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D81" s="1">
         <v>7</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(D81, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G81</f>
@@ -11528,24 +11538,24 @@
         <v>0.1</v>
       </c>
       <c r="AK81" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL81" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="82" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B82" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D82" s="1">
         <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(D82, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G82</f>
@@ -11649,24 +11659,24 @@
         <v>0.2</v>
       </c>
       <c r="AK82" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL82" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B83" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D83" s="1">
         <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(D83, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G83</f>
@@ -11770,24 +11780,24 @@
         <v>0.2</v>
       </c>
       <c r="AK83" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL83" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B84" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D84" s="1">
         <v>8</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(D84, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G84</f>
@@ -11891,24 +11901,24 @@
         <v>0.2</v>
       </c>
       <c r="AK84" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AL84" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="AL84" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="85" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B85" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D85" s="1">
         <v>8</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(D85, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G85</f>
@@ -12012,24 +12022,24 @@
         <v>0.2</v>
       </c>
       <c r="AK85" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL85" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B86" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D86" s="1">
         <v>2</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F86" s="1">
         <f>VLOOKUP(D86, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G86</f>
@@ -12133,24 +12143,24 @@
         <v>0.1</v>
       </c>
       <c r="AK86" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AL86" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B87" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F87" s="1">
         <f>VLOOKUP(D87, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G87</f>
@@ -12254,24 +12264,24 @@
         <v>0.15</v>
       </c>
       <c r="AK87" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AL87" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B88" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D88" s="1">
         <v>4</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F88" s="1">
         <f>VLOOKUP(D88, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G88</f>
@@ -12375,24 +12385,24 @@
         <v>0.15</v>
       </c>
       <c r="AK88" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AL88" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B89" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D89" s="1">
         <v>5</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F89" s="1">
         <f>VLOOKUP(D89, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G89</f>
@@ -12496,24 +12506,24 @@
         <v>0.2</v>
       </c>
       <c r="AK89" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AL89" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B90" s="1">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D90" s="1">
         <v>6</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F90" s="1">
         <f>VLOOKUP(D90, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G90</f>
@@ -12617,24 +12627,24 @@
         <v>0.2</v>
       </c>
       <c r="AK90" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AL90" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="91" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B91" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D91" s="1">
         <v>7</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F91" s="1">
         <f>VLOOKUP(D91, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G91</f>
@@ -12738,24 +12748,24 @@
         <v>0.25</v>
       </c>
       <c r="AK91" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AL91" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B92" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D92" s="1">
         <v>4</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F92" s="1">
         <f>VLOOKUP(D92, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G92</f>
@@ -12859,21 +12869,21 @@
         <v>0.05</v>
       </c>
       <c r="AK92" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B93" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D93" s="1">
         <v>6</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F93" s="1">
         <f>VLOOKUP(D93, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G93</f>
@@ -12977,24 +12987,24 @@
         <v>0.05</v>
       </c>
       <c r="AK93" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AL93" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B94" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D94" s="1">
         <v>2</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F94" s="1">
         <f>VLOOKUP(D94, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G94</f>
@@ -13098,24 +13108,24 @@
         <v>0</v>
       </c>
       <c r="AK94" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AL94" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B95" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F95" s="1">
         <f>VLOOKUP(D95, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G95</f>
@@ -13219,24 +13229,24 @@
         <v>0.15</v>
       </c>
       <c r="AK95" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AL95" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B96" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D96" s="1">
         <v>4</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F96" s="1">
         <f>VLOOKUP(D96, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G96</f>
@@ -13340,24 +13350,24 @@
         <v>0</v>
       </c>
       <c r="AK96" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AL96" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B97" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D97" s="1">
         <v>5</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F97" s="1">
         <f>VLOOKUP(D97, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G97</f>
@@ -13461,21 +13471,21 @@
         <v>0.1</v>
       </c>
       <c r="AK97" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="98" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B98" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D98" s="1">
         <v>6</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F98" s="1">
         <f>VLOOKUP(D98, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G98</f>
@@ -13579,24 +13589,24 @@
         <v>0.1</v>
       </c>
       <c r="AK98" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AL98" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B99" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D99" s="1">
         <v>7</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F99" s="1">
         <f>VLOOKUP(D99, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G99</f>
@@ -13700,24 +13710,24 @@
         <v>0.15</v>
       </c>
       <c r="AK99" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AL99" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B100" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D100" s="1">
         <v>2</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F100" s="1">
         <f>VLOOKUP(D100, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G100</f>
@@ -13821,21 +13831,21 @@
         <v>0.05</v>
       </c>
       <c r="AK100" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B101" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D101" s="1">
         <v>3</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F101" s="1">
         <f>VLOOKUP(D101, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G101</f>
@@ -13939,24 +13949,24 @@
         <v>0.05</v>
       </c>
       <c r="AK101" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AL101" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="102" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B102" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D102" s="1">
         <v>4</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F102" s="1">
         <f>VLOOKUP(D102, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G102</f>
@@ -14060,24 +14070,24 @@
         <v>0.05</v>
       </c>
       <c r="AK102" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AL102" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B103" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D103" s="1">
         <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F103" s="1">
         <f>VLOOKUP(D103, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G103</f>
@@ -14181,24 +14191,24 @@
         <v>0.05</v>
       </c>
       <c r="AK103" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AL103" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B104" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D104" s="1">
         <v>6</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F104" s="1">
         <f>VLOOKUP(D104, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G104</f>
@@ -14302,24 +14312,24 @@
         <v>0.05</v>
       </c>
       <c r="AK104" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AL104" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B105" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D105" s="1">
         <v>7</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F105" s="1">
         <f>VLOOKUP(D105, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G105</f>
@@ -14423,24 +14433,24 @@
         <v>0.1</v>
       </c>
       <c r="AK105" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AL105" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B106" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D106" s="1">
         <v>7</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F106" s="1">
         <f>VLOOKUP(D106, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G106</f>
@@ -14544,24 +14554,24 @@
         <v>0.2</v>
       </c>
       <c r="AK106" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AL106" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B107" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D107" s="1">
         <v>8</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F107" s="1">
         <f>VLOOKUP(D107, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G107</f>
@@ -14665,24 +14675,24 @@
         <v>0.1</v>
       </c>
       <c r="AK107" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AL107" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="108" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B108" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D108" s="1">
         <v>2</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F108" s="1">
         <f>VLOOKUP(D108, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G108</f>
@@ -14786,21 +14796,21 @@
         <v>0.05</v>
       </c>
       <c r="AK108" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="109" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B109" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F109" s="1">
         <f>VLOOKUP(D109, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G109</f>
@@ -14904,24 +14914,24 @@
         <v>0.05</v>
       </c>
       <c r="AK109" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL109" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="110" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B110" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D110" s="1">
         <v>4</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F110" s="1">
         <f>VLOOKUP(D110, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G110</f>
@@ -15025,24 +15035,24 @@
         <v>0.05</v>
       </c>
       <c r="AK110" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL110" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="111" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B111" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D111" s="1">
         <v>5</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F111" s="1">
         <f>VLOOKUP(D111, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G111</f>
@@ -15146,24 +15156,24 @@
         <v>0.05</v>
       </c>
       <c r="AK111" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL111" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B112" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D112" s="1">
         <v>2</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F112" s="1">
         <f>VLOOKUP(D112, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G112</f>
@@ -15267,21 +15277,21 @@
         <v>0.15</v>
       </c>
       <c r="AK112" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B113" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F113" s="1">
         <f>VLOOKUP(D113, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G113</f>
@@ -15385,21 +15395,21 @@
         <v>0.15</v>
       </c>
       <c r="AK113" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="114" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B114" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D114" s="1">
         <v>4</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F114" s="1">
         <f>VLOOKUP(D114, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G114</f>
@@ -15503,21 +15513,21 @@
         <v>0.2</v>
       </c>
       <c r="AK114" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B115" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D115" s="1">
         <v>5</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F115" s="1">
         <f>VLOOKUP(D115, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G115</f>
@@ -15621,21 +15631,21 @@
         <v>0.2</v>
       </c>
       <c r="AK115" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="116" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B116" s="1">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D116" s="1">
         <v>6</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F116" s="1">
         <f>VLOOKUP(D116, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G116</f>
@@ -15739,21 +15749,21 @@
         <v>0.25</v>
       </c>
       <c r="AK116" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B117" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D117" s="1">
         <v>7</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F117" s="1">
         <f>VLOOKUP(D117, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G117</f>
@@ -15857,21 +15867,21 @@
         <v>0.25</v>
       </c>
       <c r="AK117" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="118" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B118" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D118" s="1">
         <v>8</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F118" s="1">
         <f>VLOOKUP(D118, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G118</f>
@@ -15975,21 +15985,21 @@
         <v>0.25</v>
       </c>
       <c r="AK118" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="119" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B119" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D119" s="1">
         <v>9</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F119" s="1">
         <f>VLOOKUP(D119, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G119</f>
@@ -16093,21 +16103,21 @@
         <v>0.3</v>
       </c>
       <c r="AK119" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="120" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B120" s="1">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F120" s="1">
         <f>VLOOKUP(D120, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G120</f>
@@ -16211,24 +16221,24 @@
         <v>0</v>
       </c>
       <c r="AK120" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AL120" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="121" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B121" s="1">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D121" s="1">
         <v>4</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F121" s="1">
         <f>VLOOKUP(D121, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G121</f>
@@ -16332,24 +16342,24 @@
         <v>0.05</v>
       </c>
       <c r="AK121" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AL121" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B122" s="1">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D122" s="1">
         <v>5</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F122" s="1">
         <f>VLOOKUP(D122, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G122</f>
@@ -16453,24 +16463,24 @@
         <v>0.05</v>
       </c>
       <c r="AK122" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AL122" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="123" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B123" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D123" s="1">
         <v>6</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F123" s="1">
         <f>VLOOKUP(D123, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G123</f>
@@ -16574,24 +16584,24 @@
         <v>0.1</v>
       </c>
       <c r="AK123" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AL123" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="124" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B124" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D124" s="1">
         <v>7</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F124" s="1">
         <f>VLOOKUP(D124, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G124</f>
@@ -16695,24 +16705,24 @@
         <v>0.15</v>
       </c>
       <c r="AK124" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AL124" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B125" s="1">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D125" s="1">
         <v>2</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F125" s="1">
         <f>VLOOKUP(D125, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G125</f>
@@ -16816,24 +16826,24 @@
         <v>0.05</v>
       </c>
       <c r="AK125" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AL125" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="126" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B126" s="1">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F126" s="1">
         <f>VLOOKUP(D126, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G126</f>
@@ -16937,24 +16947,24 @@
         <v>0.15</v>
       </c>
       <c r="AK126" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AL126" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="127" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B127" s="1">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D127" s="1">
         <v>4</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F127" s="1">
         <f>VLOOKUP(D127, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G127</f>
@@ -17058,21 +17068,21 @@
         <v>0.2</v>
       </c>
       <c r="AK127" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="128" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B128" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D128" s="1">
         <v>5</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F128" s="1">
         <f>VLOOKUP(D128, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G128</f>
@@ -17176,24 +17186,24 @@
         <v>0.2</v>
       </c>
       <c r="AK128" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="AL128" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="129" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B129" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D129" s="1">
         <v>6</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F129" s="1">
         <f>VLOOKUP(D129, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G129</f>
@@ -17297,24 +17307,24 @@
         <v>0</v>
       </c>
       <c r="AK129" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AL129" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="130" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B130" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D130" s="1">
         <v>3</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F130" s="1">
         <f>VLOOKUP(D130, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G130</f>
@@ -17418,24 +17428,24 @@
         <v>0.05</v>
       </c>
       <c r="AK130" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL130" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="131" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B131" s="1">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D131" s="1">
         <v>4</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F131" s="1">
         <f>VLOOKUP(D131, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G131</f>
@@ -17539,24 +17549,24 @@
         <v>0.05</v>
       </c>
       <c r="AK131" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL131" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="132" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B132" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D132" s="1">
         <v>5</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F132" s="1">
         <f>VLOOKUP(D132, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G132</f>
@@ -17660,24 +17670,24 @@
         <v>0.2</v>
       </c>
       <c r="AK132" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL132" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="133" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B133" s="1">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D133" s="1">
         <v>2</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F133" s="1">
         <f>VLOOKUP(D133, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G133</f>
@@ -17781,21 +17791,21 @@
         <v>0</v>
       </c>
       <c r="AK133" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="134" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B134" s="1">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D134" s="1">
         <v>3</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F134" s="1">
         <f>VLOOKUP(D134, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G134</f>
@@ -17899,21 +17909,21 @@
         <v>0.05</v>
       </c>
       <c r="AK134" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="135" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B135" s="1">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D135" s="1">
         <v>4</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F135" s="1">
         <f>VLOOKUP(D135, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G135</f>
@@ -18017,24 +18027,24 @@
         <v>0.05</v>
       </c>
       <c r="AK135" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AL135" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="136" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B136" s="1">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D136" s="1">
         <v>5</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F136" s="1">
         <f>VLOOKUP(D136, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G136</f>
@@ -18138,24 +18148,24 @@
         <v>0.05</v>
       </c>
       <c r="AK136" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AL136" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="137" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B137" s="1">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D137" s="1">
         <v>6</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F137" s="1">
         <f>VLOOKUP(D137, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G137</f>
@@ -18259,21 +18269,21 @@
         <v>0.05</v>
       </c>
       <c r="AK137" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B138" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D138" s="1">
         <v>7</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F138" s="1">
         <f>VLOOKUP(D138, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G138</f>
@@ -18377,24 +18387,24 @@
         <v>0.05</v>
       </c>
       <c r="AK138" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AL138" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="139" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B139" s="1">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D139" s="1">
         <v>3</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F139" s="1">
         <f>VLOOKUP(D139, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G139</f>
@@ -18498,24 +18508,24 @@
         <v>0</v>
       </c>
       <c r="AK139" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL139" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="140" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B140" s="1">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D140" s="1">
         <v>6</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="F140" s="1">
         <f>VLOOKUP(D140, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G140</f>
@@ -18619,24 +18629,24 @@
         <v>0.1</v>
       </c>
       <c r="AK140" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AL140" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="141" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B141" s="1">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D141" s="1">
         <v>1</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="F141" s="1">
         <f>VLOOKUP(D141, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G141</f>
@@ -18740,21 +18750,21 @@
         <v>0.05</v>
       </c>
       <c r="AK141" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="142" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B142" s="1">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D142" s="1">
         <v>2</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F142" s="1">
         <f>VLOOKUP(D142, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G142</f>
@@ -18858,24 +18868,24 @@
         <v>0.1</v>
       </c>
       <c r="AK142" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AL142" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="143" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B143" s="1">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D143" s="1">
         <v>3</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="F143" s="1">
         <f>VLOOKUP(D143, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G143</f>
@@ -18979,24 +18989,24 @@
         <v>0.15</v>
       </c>
       <c r="AK143" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AL143" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="144" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B144" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D144" s="1">
         <v>4</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F144" s="1">
         <f>VLOOKUP(D144, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G144</f>
@@ -19100,24 +19110,24 @@
         <v>0.1</v>
       </c>
       <c r="AK144" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AL144" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="145" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B145" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D145" s="1">
         <v>9</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F145" s="1">
         <f>VLOOKUP(D145, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G145</f>
@@ -19221,36 +19231,36 @@
         <v>0</v>
       </c>
       <c r="AK145" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL145" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AM145" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AN145" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AO145" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AP145" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="146" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B146" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D146" s="1">
         <v>9</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F146" s="1">
         <f>VLOOKUP(D146, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G146</f>
@@ -19354,36 +19364,36 @@
         <v>0.3</v>
       </c>
       <c r="AK146" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AL146" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="AM146" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="AN146" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="AM146" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="AN146" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="AO146" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AP146" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="147" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B147" s="1">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D147" s="1">
         <v>9</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F147" s="1">
         <f>VLOOKUP(D147, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G147</f>
@@ -19487,45 +19497,45 @@
         <v>0.3</v>
       </c>
       <c r="AK147" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AL147" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="AM147" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="AN147" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AO147" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="AP147" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="AQ147" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="AR147" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AM147" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="AN147" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="AO147" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AP147" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AQ147" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="AR147" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="AS147" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="148" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B148" s="1">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D148" s="1">
         <v>9</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F148" s="1">
         <f>VLOOKUP(D148, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G148</f>
@@ -19629,33 +19639,33 @@
         <v>0.3</v>
       </c>
       <c r="AK148" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AL148" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AM148" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AN148" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AO148" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="149" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B149" s="1">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D149" s="1">
         <v>9</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F149" s="1">
         <f>VLOOKUP(D149, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G149</f>
@@ -19759,22 +19769,22 @@
         <v>0.35</v>
       </c>
       <c r="AK149" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AL149" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AM149" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AN149" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AO149" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AP149" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -19785,7 +19795,7 @@
     <mergeCell ref="AK1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F35:H149 Y5:XFD34 A5:H34 I5:X149 H6:H149">
+  <conditionalFormatting sqref="A5:H34 Y5:XFD34 I5:X149 H6:H149 B7:B149 F35:H149">
     <cfRule type="expression" priority="5">
       <formula xml:space="preserve"> MOD(ROW(),2)</formula>
     </cfRule>
@@ -19813,11 +19823,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5" xr:uid="{AF6DF336-CE2E-4FDC-86E3-D0ED4DA0E178}">
-      <formula1>"NONE,LING,XIAN,SHEN"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError sqref="L5" formula="1"/>

--- a/design/MiniTemplate/Excels/#role.xlsx
+++ b/design/MiniTemplate/Excels/#role.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BiliBili\Work\slime\design\MiniTemplate\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3997A019-F9BC-4CF3-8C91-FF86CC4400AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55AD3FA-B7CF-4B58-AEE2-BDBEB38CF841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6552" yWindow="2100" windowWidth="20952" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="470">
   <si>
     <t>##var</t>
   </si>
@@ -1017,10 +1017,6 @@
     <t>fensheng</t>
   </si>
   <si>
-    <t>RoleQuality</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RoleRelation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1043,6 +1039,445 @@
   <si>
     <t>zuie2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>h1</t>
+  </si>
+  <si>
+    <t>h2</t>
+  </si>
+  <si>
+    <t>h3</t>
+  </si>
+  <si>
+    <t>h4</t>
+  </si>
+  <si>
+    <t>h5</t>
+  </si>
+  <si>
+    <t>h6</t>
+  </si>
+  <si>
+    <t>h7</t>
+  </si>
+  <si>
+    <t>h8</t>
+  </si>
+  <si>
+    <t>h9</t>
+  </si>
+  <si>
+    <t>h10</t>
+  </si>
+  <si>
+    <t>h11</t>
+  </si>
+  <si>
+    <t>h12</t>
+  </si>
+  <si>
+    <t>h13</t>
+  </si>
+  <si>
+    <t>h14</t>
+  </si>
+  <si>
+    <t>h15</t>
+  </si>
+  <si>
+    <t>h16</t>
+  </si>
+  <si>
+    <t>h17</t>
+  </si>
+  <si>
+    <t>h18</t>
+  </si>
+  <si>
+    <t>h19</t>
+  </si>
+  <si>
+    <t>h20</t>
+  </si>
+  <si>
+    <t>h21</t>
+  </si>
+  <si>
+    <t>h22</t>
+  </si>
+  <si>
+    <t>h23</t>
+  </si>
+  <si>
+    <t>h24</t>
+  </si>
+  <si>
+    <t>h25</t>
+  </si>
+  <si>
+    <t>h26</t>
+  </si>
+  <si>
+    <t>h27</t>
+  </si>
+  <si>
+    <t>h28</t>
+  </si>
+  <si>
+    <t>h29</t>
+  </si>
+  <si>
+    <t>h30</t>
+  </si>
+  <si>
+    <t>h31</t>
+  </si>
+  <si>
+    <t>h32</t>
+  </si>
+  <si>
+    <t>h33</t>
+  </si>
+  <si>
+    <t>h34</t>
+  </si>
+  <si>
+    <t>h35</t>
+  </si>
+  <si>
+    <t>h36</t>
+  </si>
+  <si>
+    <t>h37</t>
+  </si>
+  <si>
+    <t>h38</t>
+  </si>
+  <si>
+    <t>h39</t>
+  </si>
+  <si>
+    <t>h40</t>
+  </si>
+  <si>
+    <t>h41</t>
+  </si>
+  <si>
+    <t>h42</t>
+  </si>
+  <si>
+    <t>h43</t>
+  </si>
+  <si>
+    <t>h44</t>
+  </si>
+  <si>
+    <t>h45</t>
+  </si>
+  <si>
+    <t>h46</t>
+  </si>
+  <si>
+    <t>h47</t>
+  </si>
+  <si>
+    <t>h48</t>
+  </si>
+  <si>
+    <t>h49</t>
+  </si>
+  <si>
+    <t>h50</t>
+  </si>
+  <si>
+    <t>h51</t>
+  </si>
+  <si>
+    <t>h52</t>
+  </si>
+  <si>
+    <t>h53</t>
+  </si>
+  <si>
+    <t>h54</t>
+  </si>
+  <si>
+    <t>h55</t>
+  </si>
+  <si>
+    <t>h56</t>
+  </si>
+  <si>
+    <t>h57</t>
+  </si>
+  <si>
+    <t>h58</t>
+  </si>
+  <si>
+    <t>h59</t>
+  </si>
+  <si>
+    <t>h60</t>
+  </si>
+  <si>
+    <t>h61</t>
+  </si>
+  <si>
+    <t>h62</t>
+  </si>
+  <si>
+    <t>h63</t>
+  </si>
+  <si>
+    <t>h64</t>
+  </si>
+  <si>
+    <t>h65</t>
+  </si>
+  <si>
+    <t>h66</t>
+  </si>
+  <si>
+    <t>h67</t>
+  </si>
+  <si>
+    <t>h68</t>
+  </si>
+  <si>
+    <t>h69</t>
+  </si>
+  <si>
+    <t>h70</t>
+  </si>
+  <si>
+    <t>h71</t>
+  </si>
+  <si>
+    <t>h72</t>
+  </si>
+  <si>
+    <t>h73</t>
+  </si>
+  <si>
+    <t>h74</t>
+  </si>
+  <si>
+    <t>h75</t>
+  </si>
+  <si>
+    <t>h76</t>
+  </si>
+  <si>
+    <t>h77</t>
+  </si>
+  <si>
+    <t>h78</t>
+  </si>
+  <si>
+    <t>h79</t>
+  </si>
+  <si>
+    <t>h80</t>
+  </si>
+  <si>
+    <t>h81</t>
+  </si>
+  <si>
+    <t>h82</t>
+  </si>
+  <si>
+    <t>h83</t>
+  </si>
+  <si>
+    <t>h84</t>
+  </si>
+  <si>
+    <t>h85</t>
+  </si>
+  <si>
+    <t>h86</t>
+  </si>
+  <si>
+    <t>h87</t>
+  </si>
+  <si>
+    <t>h88</t>
+  </si>
+  <si>
+    <t>h89</t>
+  </si>
+  <si>
+    <t>h90</t>
+  </si>
+  <si>
+    <t>h91</t>
+  </si>
+  <si>
+    <t>h92</t>
+  </si>
+  <si>
+    <t>h93</t>
+  </si>
+  <si>
+    <t>h94</t>
+  </si>
+  <si>
+    <t>h95</t>
+  </si>
+  <si>
+    <t>h96</t>
+  </si>
+  <si>
+    <t>h97</t>
+  </si>
+  <si>
+    <t>h98</t>
+  </si>
+  <si>
+    <t>h99</t>
+  </si>
+  <si>
+    <t>h100</t>
+  </si>
+  <si>
+    <t>h101</t>
+  </si>
+  <si>
+    <t>h102</t>
+  </si>
+  <si>
+    <t>h103</t>
+  </si>
+  <si>
+    <t>h104</t>
+  </si>
+  <si>
+    <t>h105</t>
+  </si>
+  <si>
+    <t>h106</t>
+  </si>
+  <si>
+    <t>h107</t>
+  </si>
+  <si>
+    <t>h108</t>
+  </si>
+  <si>
+    <t>h109</t>
+  </si>
+  <si>
+    <t>h110</t>
+  </si>
+  <si>
+    <t>h111</t>
+  </si>
+  <si>
+    <t>h112</t>
+  </si>
+  <si>
+    <t>h113</t>
+  </si>
+  <si>
+    <t>h114</t>
+  </si>
+  <si>
+    <t>h115</t>
+  </si>
+  <si>
+    <t>h116</t>
+  </si>
+  <si>
+    <t>h117</t>
+  </si>
+  <si>
+    <t>h118</t>
+  </si>
+  <si>
+    <t>h119</t>
+  </si>
+  <si>
+    <t>h120</t>
+  </si>
+  <si>
+    <t>h121</t>
+  </si>
+  <si>
+    <t>h122</t>
+  </si>
+  <si>
+    <t>h123</t>
+  </si>
+  <si>
+    <t>h124</t>
+  </si>
+  <si>
+    <t>h125</t>
+  </si>
+  <si>
+    <t>h126</t>
+  </si>
+  <si>
+    <t>h127</t>
+  </si>
+  <si>
+    <t>h128</t>
+  </si>
+  <si>
+    <t>h129</t>
+  </si>
+  <si>
+    <t>h130</t>
+  </si>
+  <si>
+    <t>h131</t>
+  </si>
+  <si>
+    <t>h132</t>
+  </si>
+  <si>
+    <t>h133</t>
+  </si>
+  <si>
+    <t>h134</t>
+  </si>
+  <si>
+    <t>h135</t>
+  </si>
+  <si>
+    <t>h136</t>
+  </si>
+  <si>
+    <t>h137</t>
+  </si>
+  <si>
+    <t>h138</t>
+  </si>
+  <si>
+    <t>h139</t>
+  </si>
+  <si>
+    <t>h140</t>
+  </si>
+  <si>
+    <t>h141</t>
+  </si>
+  <si>
+    <t>h142</t>
+  </si>
+  <si>
+    <t>h143</t>
+  </si>
+  <si>
+    <t>h144</t>
+  </si>
+  <si>
+    <t>h145</t>
   </si>
 </sst>
 </file>
@@ -2046,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>324</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -2055,7 +2490,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>26</v>
@@ -2091,7 +2526,7 @@
         <v>210</v>
       </c>
       <c r="Y2" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Z2" s="14"/>
       <c r="AA2" s="14"/>
@@ -2288,8 +2723,8 @@
       </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B5" s="1">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>23</v>
@@ -2298,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(D5, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G5</f>
@@ -2368,46 +2803,13 @@
       <c r="X5" s="1">
         <v>1</v>
       </c>
-      <c r="Y5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="1">
-        <v>0</v>
-      </c>
       <c r="AK5" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B6" s="1">
-        <v>2</v>
+      <c r="B6" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>43</v>
@@ -2416,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(D6, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G6</f>
@@ -2489,43 +2891,16 @@
       <c r="Y6" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z6" s="1">
-        <v>0</v>
-      </c>
       <c r="AA6" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="1">
-        <v>0</v>
-      </c>
       <c r="AK6" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B7" s="1">
-        <v>3</v>
+      <c r="B7" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>44</v>
@@ -2534,7 +2909,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(D7, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G7</f>
@@ -2607,43 +2982,16 @@
       <c r="Y7" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
       <c r="AA7" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="1">
-        <v>0</v>
-      </c>
       <c r="AK7" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B8" s="1">
-        <v>4</v>
+      <c r="B8" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>45</v>
@@ -2652,7 +3000,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(D8, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G8</f>
@@ -2725,43 +3073,16 @@
       <c r="Y8" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
       <c r="AA8" s="1">
         <v>0.6</v>
       </c>
-      <c r="AB8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="1">
-        <v>0</v>
-      </c>
       <c r="AK8" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B9" s="1">
-        <v>5</v>
+      <c r="B9" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
@@ -2770,7 +3091,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(D9, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G9</f>
@@ -2843,43 +3164,19 @@
       <c r="Y9" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z9" s="1">
-        <v>0</v>
-      </c>
       <c r="AA9" s="1">
         <v>0.6</v>
       </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>0</v>
-      </c>
       <c r="AH9" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AI9" s="1">
-        <v>0</v>
       </c>
       <c r="AK9" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B10" s="1">
-        <v>6</v>
+      <c r="B10" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -2888,7 +3185,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(D10, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G10</f>
@@ -2961,35 +3258,14 @@
       <c r="Y10" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z10" s="1">
-        <v>0</v>
-      </c>
       <c r="AA10" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="1">
-        <v>0</v>
-      </c>
       <c r="AF10" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG10" s="1">
-        <v>0</v>
-      </c>
       <c r="AH10" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AI10" s="1">
-        <v>0</v>
       </c>
       <c r="AK10" s="1" t="s">
         <v>221</v>
@@ -2999,8 +3275,8 @@
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B11" s="1">
-        <v>7</v>
+      <c r="B11" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>48</v>
@@ -3009,7 +3285,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(D11, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G11</f>
@@ -3082,35 +3358,14 @@
       <c r="Y11" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z11" s="1">
-        <v>0</v>
-      </c>
       <c r="AA11" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="1">
-        <v>0</v>
-      </c>
       <c r="AF11" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG11" s="1">
-        <v>0</v>
-      </c>
       <c r="AH11" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AI11" s="1">
-        <v>0</v>
       </c>
       <c r="AK11" s="1" t="s">
         <v>221</v>
@@ -3120,8 +3375,8 @@
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B12" s="1">
-        <v>8</v>
+      <c r="B12" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>49</v>
@@ -3130,7 +3385,7 @@
         <v>7</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(D12, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G12</f>
@@ -3203,30 +3458,12 @@
       <c r="Y12" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
       <c r="AA12" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>0</v>
-      </c>
       <c r="AF12" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG12" s="1">
-        <v>0</v>
-      </c>
       <c r="AH12" s="1">
         <v>0.1</v>
       </c>
@@ -3241,8 +3478,8 @@
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B13" s="1">
-        <v>9</v>
+      <c r="B13" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>50</v>
@@ -3251,7 +3488,7 @@
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(D13, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G13</f>
@@ -3324,30 +3561,15 @@
       <c r="Y13" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
       <c r="AA13" s="1">
         <v>0.4</v>
       </c>
-      <c r="AB13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>0</v>
-      </c>
       <c r="AE13" s="1">
         <v>0.1</v>
       </c>
       <c r="AF13" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG13" s="1">
-        <v>0</v>
-      </c>
       <c r="AH13" s="1">
         <v>0.15</v>
       </c>
@@ -3362,8 +3584,8 @@
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B14" s="1">
-        <v>10</v>
+      <c r="B14" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>51</v>
@@ -3372,7 +3594,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(D14, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G14</f>
@@ -3445,30 +3667,12 @@
       <c r="Y14" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
       <c r="AA14" s="1">
         <v>0.4</v>
       </c>
-      <c r="AB14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="1">
-        <v>0</v>
-      </c>
       <c r="AF14" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG14" s="1">
-        <v>0</v>
-      </c>
       <c r="AH14" s="1">
         <v>0.1</v>
       </c>
@@ -3483,8 +3687,8 @@
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B15" s="1">
-        <v>11</v>
+      <c r="B15" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>52</v>
@@ -3493,7 +3697,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(D15, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G15</f>
@@ -3566,30 +3770,12 @@
       <c r="Y15" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
       <c r="AA15" s="1">
         <v>0.4</v>
       </c>
-      <c r="AB15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="1">
-        <v>0</v>
-      </c>
       <c r="AF15" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG15" s="1">
-        <v>0</v>
-      </c>
       <c r="AH15" s="1">
         <v>0.15</v>
       </c>
@@ -3604,8 +3790,8 @@
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="B16" s="1">
-        <v>12</v>
+      <c r="B16" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>53</v>
@@ -3614,7 +3800,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(D16, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G16</f>
@@ -3687,30 +3873,12 @@
       <c r="Y16" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z16" s="1">
-        <v>0</v>
-      </c>
       <c r="AA16" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="1">
-        <v>0</v>
-      </c>
       <c r="AF16" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG16" s="1">
-        <v>0</v>
-      </c>
       <c r="AH16" s="1">
         <v>0.15</v>
       </c>
@@ -3725,8 +3893,8 @@
       </c>
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B17" s="1">
-        <v>13</v>
+      <c r="B17" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>54</v>
@@ -3735,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(D17, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G17</f>
@@ -3805,23 +3973,8 @@
       <c r="X17" s="1">
         <v>0.9</v>
       </c>
-      <c r="Y17" s="1">
-        <v>0</v>
-      </c>
       <c r="Z17" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>0</v>
       </c>
       <c r="AE17" s="1">
         <v>0.5</v>
@@ -3829,22 +3982,13 @@
       <c r="AF17" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="1">
-        <v>0</v>
-      </c>
       <c r="AK17" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B18" s="1">
-        <v>14</v>
+      <c r="B18" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>55</v>
@@ -3853,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(D18, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G18</f>
@@ -3923,23 +4067,8 @@
       <c r="X18" s="1">
         <v>1</v>
       </c>
-      <c r="Y18" s="1">
-        <v>0</v>
-      </c>
       <c r="Z18" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>0</v>
       </c>
       <c r="AE18" s="1">
         <v>0.4</v>
@@ -3947,22 +4076,13 @@
       <c r="AF18" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="1">
-        <v>0</v>
-      </c>
       <c r="AK18" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="19" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B19" s="1">
-        <v>15</v>
+      <c r="B19" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>56</v>
@@ -3971,7 +4091,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(D19, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G19</f>
@@ -4041,23 +4161,8 @@
       <c r="X19" s="1">
         <v>1</v>
       </c>
-      <c r="Y19" s="1">
-        <v>0</v>
-      </c>
       <c r="Z19" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="1">
-        <v>0</v>
       </c>
       <c r="AE19" s="1">
         <v>0.6</v>
@@ -4065,22 +4170,13 @@
       <c r="AF19" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="1">
-        <v>0</v>
-      </c>
       <c r="AK19" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="20" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B20" s="1">
-        <v>16</v>
+      <c r="B20" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>57</v>
@@ -4089,7 +4185,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(D20, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G20</f>
@@ -4159,36 +4255,15 @@
       <c r="X20" s="1">
         <v>1</v>
       </c>
-      <c r="Y20" s="1">
-        <v>0</v>
-      </c>
       <c r="Z20" s="1">
         <v>0.2</v>
       </c>
-      <c r="AA20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="1">
-        <v>0</v>
-      </c>
       <c r="AE20" s="1">
         <v>0.5</v>
       </c>
       <c r="AF20" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="1">
-        <v>0</v>
-      </c>
       <c r="AI20" s="1">
         <v>0.1</v>
       </c>
@@ -4200,8 +4275,8 @@
       </c>
     </row>
     <row r="21" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B21" s="1">
-        <v>17</v>
+      <c r="B21" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>58</v>
@@ -4210,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(D21, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G21</f>
@@ -4286,33 +4361,12 @@
       <c r="Z21" s="1">
         <v>0.2</v>
       </c>
-      <c r="AA21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>0</v>
-      </c>
       <c r="AE21" s="1">
         <v>0.5</v>
       </c>
       <c r="AF21" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="1">
-        <v>0</v>
-      </c>
       <c r="AK21" s="1" t="s">
         <v>228</v>
       </c>
@@ -4321,8 +4375,8 @@
       </c>
     </row>
     <row r="22" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B22" s="1">
-        <v>18</v>
+      <c r="B22" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>59</v>
@@ -4331,7 +4385,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(D22, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G22</f>
@@ -4401,23 +4455,8 @@
       <c r="X22" s="1">
         <v>1</v>
       </c>
-      <c r="Y22" s="1">
-        <v>0</v>
-      </c>
       <c r="Z22" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="1">
-        <v>0</v>
       </c>
       <c r="AE22" s="1">
         <v>0.5</v>
@@ -4425,15 +4464,6 @@
       <c r="AF22" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="1">
-        <v>0</v>
-      </c>
       <c r="AK22" s="1" t="s">
         <v>224</v>
       </c>
@@ -4442,8 +4472,8 @@
       </c>
     </row>
     <row r="23" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B23" s="1">
-        <v>19</v>
+      <c r="B23" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>60</v>
@@ -4452,7 +4482,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(D23, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G23</f>
@@ -4522,23 +4552,8 @@
       <c r="X23" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y23" s="1">
-        <v>0</v>
-      </c>
       <c r="Z23" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>0</v>
       </c>
       <c r="AE23" s="1">
         <v>0.7</v>
@@ -4546,15 +4561,6 @@
       <c r="AF23" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="1">
-        <v>0</v>
-      </c>
       <c r="AK23" s="1" t="s">
         <v>224</v>
       </c>
@@ -4563,8 +4569,8 @@
       </c>
     </row>
     <row r="24" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B24" s="1">
-        <v>20</v>
+      <c r="B24" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>61</v>
@@ -4573,7 +4579,7 @@
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(D24, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G24</f>
@@ -4643,23 +4649,8 @@
       <c r="X24" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y24" s="1">
-        <v>0</v>
-      </c>
       <c r="Z24" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>0</v>
       </c>
       <c r="AE24" s="1">
         <v>0.6</v>
@@ -4667,22 +4658,13 @@
       <c r="AF24" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="1">
-        <v>0</v>
-      </c>
       <c r="AK24" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="25" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B25" s="1">
-        <v>21</v>
+      <c r="B25" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>62</v>
@@ -4691,7 +4673,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(D25, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G25</f>
@@ -4761,23 +4743,8 @@
       <c r="X25" s="1">
         <v>1</v>
       </c>
-      <c r="Y25" s="1">
-        <v>0</v>
-      </c>
       <c r="Z25" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="1">
-        <v>0</v>
       </c>
       <c r="AE25" s="1">
         <v>0.5</v>
@@ -4785,15 +4752,6 @@
       <c r="AF25" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="1">
-        <v>0</v>
-      </c>
       <c r="AK25" s="1" t="s">
         <v>224</v>
       </c>
@@ -4802,8 +4760,8 @@
       </c>
     </row>
     <row r="26" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B26" s="1">
-        <v>22</v>
+      <c r="B26" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>63</v>
@@ -4812,7 +4770,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(D26, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G26</f>
@@ -4882,23 +4840,8 @@
       <c r="X26" s="1">
         <v>1</v>
       </c>
-      <c r="Y26" s="1">
-        <v>0</v>
-      </c>
       <c r="Z26" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>0</v>
       </c>
       <c r="AE26" s="1">
         <v>0.6</v>
@@ -4906,22 +4849,13 @@
       <c r="AF26" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="1">
-        <v>0</v>
-      </c>
       <c r="AK26" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="27" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B27" s="1">
-        <v>23</v>
+      <c r="B27" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
@@ -4930,7 +4864,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(D27, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G27</f>
@@ -5000,23 +4934,8 @@
       <c r="X27" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y27" s="1">
-        <v>0</v>
-      </c>
       <c r="Z27" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>0</v>
       </c>
       <c r="AE27" s="1">
         <v>0.7</v>
@@ -5024,15 +4943,6 @@
       <c r="AF27" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="1">
-        <v>0</v>
-      </c>
       <c r="AK27" s="1" t="s">
         <v>231</v>
       </c>
@@ -5041,8 +4951,8 @@
       </c>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B28" s="1">
-        <v>24</v>
+      <c r="B28" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
@@ -5051,7 +4961,7 @@
         <v>7</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(D28, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G28</f>
@@ -5121,23 +5031,8 @@
       <c r="X28" s="1">
         <v>1</v>
       </c>
-      <c r="Y28" s="1">
-        <v>0</v>
-      </c>
       <c r="Z28" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>0</v>
       </c>
       <c r="AE28" s="1">
         <v>0.7</v>
@@ -5145,12 +5040,6 @@
       <c r="AF28" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="1">
-        <v>0</v>
-      </c>
       <c r="AI28" s="1">
         <v>0.1</v>
       </c>
@@ -5162,8 +5051,8 @@
       </c>
     </row>
     <row r="29" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B29" s="1">
-        <v>25</v>
+      <c r="B29" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>66</v>
@@ -5172,7 +5061,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(D29, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G29</f>
@@ -5242,23 +5131,8 @@
       <c r="X29" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y29" s="1">
-        <v>0</v>
-      </c>
       <c r="Z29" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>0</v>
       </c>
       <c r="AE29" s="1">
         <v>0.6</v>
@@ -5266,12 +5140,6 @@
       <c r="AF29" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="1">
-        <v>0</v>
-      </c>
       <c r="AI29" s="1">
         <v>0.1</v>
       </c>
@@ -5283,8 +5151,8 @@
       </c>
     </row>
     <row r="30" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B30" s="1">
-        <v>26</v>
+      <c r="B30" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>67</v>
@@ -5293,7 +5161,7 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(D30, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G30</f>
@@ -5363,23 +5231,8 @@
       <c r="X30" s="1">
         <v>1</v>
       </c>
-      <c r="Y30" s="1">
-        <v>0</v>
-      </c>
       <c r="Z30" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="1">
-        <v>0</v>
       </c>
       <c r="AE30" s="1">
         <v>0.7</v>
@@ -5387,12 +5240,6 @@
       <c r="AF30" s="1">
         <v>0.05</v>
       </c>
-      <c r="AG30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH30" s="1">
-        <v>0</v>
-      </c>
       <c r="AI30" s="1">
         <v>0.1</v>
       </c>
@@ -5404,8 +5251,8 @@
       </c>
     </row>
     <row r="31" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B31" s="1">
-        <v>27</v>
+      <c r="B31" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>68</v>
@@ -5414,7 +5261,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(D31, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G31</f>
@@ -5484,23 +5331,8 @@
       <c r="X31" s="1">
         <v>1.2</v>
       </c>
-      <c r="Y31" s="1">
-        <v>0</v>
-      </c>
       <c r="Z31" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>0</v>
       </c>
       <c r="AE31" s="1">
         <v>0.6</v>
@@ -5508,12 +5340,6 @@
       <c r="AF31" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="1">
-        <v>0</v>
-      </c>
       <c r="AI31" s="1">
         <v>0.2</v>
       </c>
@@ -5525,8 +5351,8 @@
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B32" s="1">
-        <v>28</v>
+      <c r="B32" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>69</v>
@@ -5535,7 +5361,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(D32, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G32</f>
@@ -5608,43 +5434,19 @@
       <c r="Y32" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1">
-        <v>0</v>
-      </c>
       <c r="AB32" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="1">
-        <v>0</v>
-      </c>
       <c r="AF32" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="1">
-        <v>0</v>
-      </c>
       <c r="AK32" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B33" s="1">
-        <v>29</v>
+      <c r="B33" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>70</v>
@@ -5653,7 +5455,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(D33, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G33</f>
@@ -5726,36 +5528,12 @@
       <c r="Y33" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="1">
-        <v>0</v>
-      </c>
       <c r="AB33" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="1">
-        <v>0</v>
-      </c>
       <c r="AF33" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="1">
-        <v>0</v>
-      </c>
       <c r="AK33" s="1" t="s">
         <v>238</v>
       </c>
@@ -5764,8 +5542,8 @@
       </c>
     </row>
     <row r="34" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B34" s="1">
-        <v>30</v>
+      <c r="B34" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>71</v>
@@ -5774,7 +5552,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(D34, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G34</f>
@@ -5847,36 +5625,12 @@
       <c r="Y34" s="1">
         <v>0.2</v>
       </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="1">
-        <v>0</v>
-      </c>
       <c r="AB34" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="1">
-        <v>0</v>
-      </c>
       <c r="AF34" s="1">
         <v>0.2</v>
       </c>
-      <c r="AG34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="1">
-        <v>0</v>
-      </c>
       <c r="AK34" s="1" t="s">
         <v>238</v>
       </c>
@@ -5885,8 +5639,8 @@
       </c>
     </row>
     <row r="35" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B35" s="1">
-        <v>31</v>
+      <c r="B35" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>72</v>
@@ -5895,7 +5649,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(D35, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G35</f>
@@ -5968,36 +5722,12 @@
       <c r="Y35" s="1">
         <v>0.2</v>
       </c>
-      <c r="Z35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="1">
-        <v>0</v>
-      </c>
       <c r="AB35" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="1">
-        <v>0</v>
-      </c>
       <c r="AF35" s="1">
         <v>0.2</v>
       </c>
-      <c r="AG35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="1">
-        <v>0</v>
-      </c>
       <c r="AK35" s="1" t="s">
         <v>238</v>
       </c>
@@ -6006,8 +5736,8 @@
       </c>
     </row>
     <row r="36" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B36" s="1">
-        <v>32</v>
+      <c r="B36" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>73</v>
@@ -6016,7 +5746,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(D36, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G36</f>
@@ -6089,36 +5819,15 @@
       <c r="Y36" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
       <c r="AB36" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>0</v>
-      </c>
       <c r="AE36" s="1">
         <v>0.15</v>
       </c>
       <c r="AF36" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI36" s="1">
-        <v>0</v>
-      </c>
       <c r="AK36" s="1" t="s">
         <v>239</v>
       </c>
@@ -6127,8 +5836,8 @@
       </c>
     </row>
     <row r="37" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B37" s="1">
-        <v>33</v>
+      <c r="B37" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>74</v>
@@ -6137,7 +5846,7 @@
         <v>7</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(D37, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G37</f>
@@ -6210,33 +5919,12 @@
       <c r="Y37" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="1">
-        <v>0</v>
-      </c>
       <c r="AB37" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="1">
-        <v>0</v>
-      </c>
       <c r="AF37" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="1">
-        <v>0</v>
-      </c>
       <c r="AI37" s="1">
         <v>0.2</v>
       </c>
@@ -6248,8 +5936,8 @@
       </c>
     </row>
     <row r="38" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B38" s="1">
-        <v>34</v>
+      <c r="B38" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>75</v>
@@ -6258,7 +5946,7 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(D38, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G38</f>
@@ -6331,33 +6019,15 @@
       <c r="Y38" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="1">
-        <v>0</v>
-      </c>
       <c r="AB38" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="1">
-        <v>0</v>
-      </c>
       <c r="AE38" s="1">
         <v>0.15</v>
       </c>
       <c r="AF38" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="1">
-        <v>0</v>
-      </c>
       <c r="AI38" s="1">
         <v>0.1</v>
       </c>
@@ -6369,8 +6039,8 @@
       </c>
     </row>
     <row r="39" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B39" s="1">
-        <v>35</v>
+      <c r="B39" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>76</v>
@@ -6379,7 +6049,7 @@
         <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(D39, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G39</f>
@@ -6452,33 +6122,12 @@
       <c r="Y39" s="1">
         <v>0.2</v>
       </c>
-      <c r="Z39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="1">
-        <v>0</v>
-      </c>
       <c r="AB39" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="1">
-        <v>0</v>
-      </c>
       <c r="AF39" s="1">
         <v>0.2</v>
       </c>
-      <c r="AG39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="1">
-        <v>0</v>
-      </c>
       <c r="AI39" s="1">
         <v>0.2</v>
       </c>
@@ -6490,8 +6139,8 @@
       </c>
     </row>
     <row r="40" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B40" s="1">
-        <v>36</v>
+      <c r="B40" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>77</v>
@@ -6500,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(D40, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G40</f>
@@ -6576,40 +6225,19 @@
       <c r="Z40" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="1">
-        <v>0</v>
-      </c>
       <c r="AC40" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="1">
-        <v>0</v>
-      </c>
       <c r="AF40" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI40" s="1">
-        <v>0</v>
       </c>
       <c r="AK40" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="41" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B41" s="1">
-        <v>37</v>
+      <c r="B41" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>78</v>
@@ -6618,7 +6246,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(D41, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G41</f>
@@ -6694,40 +6322,19 @@
       <c r="Z41" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="1">
-        <v>0</v>
-      </c>
       <c r="AC41" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="1">
-        <v>0</v>
-      </c>
       <c r="AF41" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI41" s="1">
-        <v>0</v>
       </c>
       <c r="AK41" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="42" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B42" s="1">
-        <v>38</v>
+      <c r="B42" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>79</v>
@@ -6736,7 +6343,7 @@
         <v>3</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(D42, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G42</f>
@@ -6812,40 +6419,19 @@
       <c r="Z42" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="1">
-        <v>0</v>
-      </c>
       <c r="AC42" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="1">
-        <v>0</v>
-      </c>
       <c r="AF42" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="1">
-        <v>0</v>
       </c>
       <c r="AK42" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="43" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B43" s="1">
-        <v>39</v>
+      <c r="B43" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>80</v>
@@ -6854,7 +6440,7 @@
         <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(D43, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G43</f>
@@ -6930,29 +6516,11 @@
       <c r="Z43" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="1">
-        <v>0</v>
-      </c>
       <c r="AC43" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="1">
-        <v>0</v>
-      </c>
       <c r="AF43" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="1">
-        <v>0</v>
       </c>
       <c r="AI43" s="1">
         <v>0.05</v>
@@ -6965,8 +6533,8 @@
       </c>
     </row>
     <row r="44" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B44" s="1">
-        <v>40</v>
+      <c r="B44" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>81</v>
@@ -6975,7 +6543,7 @@
         <v>5</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(D44, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G44</f>
@@ -7051,29 +6619,11 @@
       <c r="Z44" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="1">
-        <v>0</v>
-      </c>
       <c r="AC44" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="1">
-        <v>0</v>
-      </c>
       <c r="AF44" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="1">
-        <v>0</v>
       </c>
       <c r="AI44" s="1">
         <v>0.1</v>
@@ -7086,8 +6636,8 @@
       </c>
     </row>
     <row r="45" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B45" s="1">
-        <v>41</v>
+      <c r="B45" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>82</v>
@@ -7096,7 +6646,7 @@
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(D45, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G45</f>
@@ -7175,26 +6725,11 @@
       <c r="AA45" s="1">
         <v>0.15</v>
       </c>
-      <c r="AB45" s="1">
-        <v>0</v>
-      </c>
       <c r="AC45" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="1">
-        <v>0</v>
-      </c>
       <c r="AF45" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="1">
-        <v>0</v>
       </c>
       <c r="AI45" s="1">
         <v>0.1</v>
@@ -7207,8 +6742,8 @@
       </c>
     </row>
     <row r="46" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B46" s="1">
-        <v>42</v>
+      <c r="B46" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>83</v>
@@ -7217,7 +6752,7 @@
         <v>7</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(D46, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G46</f>
@@ -7293,26 +6828,11 @@
       <c r="Z46" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="1">
-        <v>0</v>
-      </c>
       <c r="AC46" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="1">
-        <v>0</v>
-      </c>
       <c r="AF46" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG46" s="1">
-        <v>0</v>
       </c>
       <c r="AH46" s="1">
         <v>0.1</v>
@@ -7328,8 +6848,8 @@
       </c>
     </row>
     <row r="47" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B47" s="1">
-        <v>43</v>
+      <c r="B47" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>84</v>
@@ -7338,7 +6858,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(D47, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G47</f>
@@ -7414,29 +6934,11 @@
       <c r="Z47" s="1">
         <v>0.1</v>
       </c>
-      <c r="AA47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="1">
-        <v>0</v>
-      </c>
       <c r="AC47" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="1">
-        <v>0</v>
-      </c>
       <c r="AF47" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="1">
-        <v>0</v>
       </c>
       <c r="AI47" s="1">
         <v>0.1</v>
@@ -7449,8 +6951,8 @@
       </c>
     </row>
     <row r="48" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B48" s="1">
-        <v>44</v>
+      <c r="B48" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>85</v>
@@ -7459,7 +6961,7 @@
         <v>9</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(D48, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G48</f>
@@ -7538,26 +7040,11 @@
       <c r="AA48" s="1">
         <v>0.15</v>
       </c>
-      <c r="AB48" s="1">
-        <v>0</v>
-      </c>
       <c r="AC48" s="1">
         <v>0.5</v>
       </c>
-      <c r="AD48" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="1">
-        <v>0</v>
-      </c>
       <c r="AF48" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG48" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="1">
-        <v>0</v>
       </c>
       <c r="AI48" s="1">
         <v>0.1</v>
@@ -7570,8 +7057,8 @@
       </c>
     </row>
     <row r="49" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B49" s="1">
-        <v>45</v>
+      <c r="B49" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>86</v>
@@ -7580,7 +7067,7 @@
         <v>2</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(D49, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G49</f>
@@ -7653,43 +7140,22 @@
       <c r="Y49" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="1">
-        <v>0</v>
-      </c>
       <c r="AB49" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="1">
-        <v>0</v>
-      </c>
       <c r="AG49" s="1">
         <v>0.1</v>
       </c>
       <c r="AH49" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AI49" s="1">
-        <v>0</v>
       </c>
       <c r="AK49" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="50" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B50" s="1">
-        <v>46</v>
+      <c r="B50" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>87</v>
@@ -7698,7 +7164,7 @@
         <v>3</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(D50, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G50</f>
@@ -7771,36 +7237,15 @@
       <c r="Y50" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="1">
-        <v>0</v>
-      </c>
       <c r="AB50" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="1">
-        <v>0</v>
-      </c>
       <c r="AG50" s="1">
         <v>0.1</v>
       </c>
       <c r="AH50" s="1">
         <v>0.2</v>
       </c>
-      <c r="AI50" s="1">
-        <v>0</v>
-      </c>
       <c r="AK50" s="1" t="s">
         <v>246</v>
       </c>
@@ -7809,8 +7254,8 @@
       </c>
     </row>
     <row r="51" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B51" s="1">
-        <v>47</v>
+      <c r="B51" s="1" t="s">
+        <v>371</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>88</v>
@@ -7819,7 +7264,7 @@
         <v>4</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(D51, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G51</f>
@@ -7892,36 +7337,15 @@
       <c r="Y51" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="1">
-        <v>0</v>
-      </c>
       <c r="AB51" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="1">
-        <v>0</v>
-      </c>
       <c r="AG51" s="1">
         <v>0.1</v>
       </c>
       <c r="AH51" s="1">
         <v>0.2</v>
       </c>
-      <c r="AI51" s="1">
-        <v>0</v>
-      </c>
       <c r="AK51" s="1" t="s">
         <v>246</v>
       </c>
@@ -7930,8 +7354,8 @@
       </c>
     </row>
     <row r="52" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B52" s="1">
-        <v>48</v>
+      <c r="B52" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>89</v>
@@ -7940,7 +7364,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(D52, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G52</f>
@@ -8013,27 +7437,9 @@
       <c r="Y52" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="1">
-        <v>0</v>
-      </c>
       <c r="AB52" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="1">
-        <v>0</v>
-      </c>
       <c r="AG52" s="1">
         <v>0.1</v>
       </c>
@@ -8051,8 +7457,8 @@
       </c>
     </row>
     <row r="53" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B53" s="1">
-        <v>49</v>
+      <c r="B53" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>90</v>
@@ -8061,7 +7467,7 @@
         <v>6</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(D53, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G53</f>
@@ -8134,27 +7540,9 @@
       <c r="Y53" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="1">
-        <v>0</v>
-      </c>
       <c r="AB53" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="1">
-        <v>0</v>
-      </c>
       <c r="AG53" s="1">
         <v>0.1</v>
       </c>
@@ -8169,8 +7557,8 @@
       </c>
     </row>
     <row r="54" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B54" s="1">
-        <v>50</v>
+      <c r="B54" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>91</v>
@@ -8179,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(D54, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G54</f>
@@ -8252,27 +7640,9 @@
       <c r="Y54" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z54" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="1">
-        <v>0</v>
-      </c>
       <c r="AB54" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC54" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="1">
-        <v>0</v>
-      </c>
       <c r="AG54" s="1">
         <v>0.1</v>
       </c>
@@ -8290,8 +7660,8 @@
       </c>
     </row>
     <row r="55" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B55" s="1">
-        <v>51</v>
+      <c r="B55" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>92</v>
@@ -8300,7 +7670,7 @@
         <v>8</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(D55, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G55</f>
@@ -8373,24 +7743,9 @@
       <c r="Y55" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="1">
-        <v>0</v>
-      </c>
       <c r="AB55" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="1">
-        <v>0</v>
-      </c>
       <c r="AF55" s="1">
         <v>0.1</v>
       </c>
@@ -8408,8 +7763,8 @@
       </c>
     </row>
     <row r="56" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B56" s="1">
-        <v>52</v>
+      <c r="B56" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>93</v>
@@ -8418,7 +7773,7 @@
         <v>9</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(D56, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G56</f>
@@ -8491,27 +7846,9 @@
       <c r="Y56" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z56" s="1">
-        <v>0</v>
-      </c>
       <c r="AA56" s="1">
         <v>0.4</v>
       </c>
-      <c r="AB56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="1">
-        <v>0</v>
-      </c>
       <c r="AG56" s="1">
         <v>0.1</v>
       </c>
@@ -8529,8 +7866,8 @@
       </c>
     </row>
     <row r="57" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B57" s="1">
-        <v>53</v>
+      <c r="B57" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>94</v>
@@ -8539,7 +7876,7 @@
         <v>3</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(D57, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G57</f>
@@ -8612,35 +7949,11 @@
       <c r="Y57" s="1">
         <v>0.2</v>
       </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="1">
-        <v>0</v>
-      </c>
       <c r="AD57" s="1">
         <v>0.5</v>
       </c>
-      <c r="AE57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="1">
-        <v>0</v>
-      </c>
       <c r="AG57" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="1">
-        <v>0</v>
       </c>
       <c r="AK57" s="1" t="s">
         <v>220</v>
@@ -8650,8 +7963,8 @@
       </c>
     </row>
     <row r="58" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B58" s="1">
-        <v>54</v>
+      <c r="B58" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>95</v>
@@ -8660,7 +7973,7 @@
         <v>5</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(D58, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G58</f>
@@ -8733,32 +8046,11 @@
       <c r="Y58" s="1">
         <v>0.2</v>
       </c>
-      <c r="Z58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="1">
-        <v>0</v>
-      </c>
       <c r="AD58" s="1">
         <v>0.5</v>
       </c>
-      <c r="AE58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="1">
-        <v>0</v>
-      </c>
       <c r="AG58" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH58" s="1">
-        <v>0</v>
       </c>
       <c r="AI58" s="1">
         <v>0.1</v>
@@ -8771,8 +8063,8 @@
       </c>
     </row>
     <row r="59" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B59" s="1">
-        <v>55</v>
+      <c r="B59" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>96</v>
@@ -8781,7 +8073,7 @@
         <v>2</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(D59, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G59</f>
@@ -8854,43 +8146,22 @@
       <c r="Y59" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="1">
-        <v>0</v>
-      </c>
       <c r="AB59" s="1">
         <v>0.25</v>
       </c>
-      <c r="AC59" s="1">
-        <v>0</v>
-      </c>
       <c r="AD59" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="1">
-        <v>0</v>
-      </c>
       <c r="AG59" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI59" s="1">
-        <v>0</v>
       </c>
       <c r="AK59" s="1" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="60" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B60" s="1">
-        <v>56</v>
+      <c r="B60" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>97</v>
@@ -8899,7 +8170,7 @@
         <v>3</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(D60, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G60</f>
@@ -8972,35 +8243,14 @@
       <c r="Y60" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="1">
-        <v>0</v>
-      </c>
       <c r="AB60" s="1">
         <v>0.25</v>
       </c>
-      <c r="AC60" s="1">
-        <v>0</v>
-      </c>
       <c r="AD60" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="1">
-        <v>0</v>
-      </c>
       <c r="AG60" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI60" s="1">
-        <v>0</v>
       </c>
       <c r="AK60" s="1" t="s">
         <v>248</v>
@@ -9010,8 +8260,8 @@
       </c>
     </row>
     <row r="61" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B61" s="1">
-        <v>57</v>
+      <c r="B61" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>98</v>
@@ -9020,7 +8270,7 @@
         <v>4</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(D61, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G61</f>
@@ -9093,35 +8343,14 @@
       <c r="Y61" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z61" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="1">
-        <v>0</v>
-      </c>
       <c r="AB61" s="1">
         <v>0.25</v>
       </c>
-      <c r="AC61" s="1">
-        <v>0</v>
-      </c>
       <c r="AD61" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE61" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="1">
-        <v>0</v>
-      </c>
       <c r="AG61" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH61" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="1">
-        <v>0</v>
       </c>
       <c r="AK61" s="1" t="s">
         <v>248</v>
@@ -9131,8 +8360,8 @@
       </c>
     </row>
     <row r="62" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B62" s="1">
-        <v>58</v>
+      <c r="B62" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>99</v>
@@ -9141,7 +8370,7 @@
         <v>5</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(D62, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G62</f>
@@ -9214,35 +8443,17 @@
       <c r="Y62" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z62" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="1">
-        <v>0</v>
-      </c>
       <c r="AB62" s="1">
         <v>0.25</v>
       </c>
-      <c r="AC62" s="1">
-        <v>0</v>
-      </c>
       <c r="AD62" s="1">
         <v>0.25</v>
       </c>
       <c r="AE62" s="1">
         <v>0.15</v>
       </c>
-      <c r="AF62" s="1">
-        <v>0</v>
-      </c>
       <c r="AG62" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH62" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI62" s="1">
-        <v>0</v>
       </c>
       <c r="AK62" s="1" t="s">
         <v>224</v>
@@ -9252,8 +8463,8 @@
       </c>
     </row>
     <row r="63" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B63" s="1">
-        <v>59</v>
+      <c r="B63" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>100</v>
@@ -9262,7 +8473,7 @@
         <v>6</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(D63, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G63</f>
@@ -9335,32 +8546,17 @@
       <c r="Y63" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="1">
-        <v>0</v>
-      </c>
       <c r="AB63" s="1">
         <v>0.25</v>
       </c>
-      <c r="AC63" s="1">
-        <v>0</v>
-      </c>
       <c r="AD63" s="1">
         <v>0.25</v>
       </c>
       <c r="AE63" s="1">
         <v>0.15</v>
       </c>
-      <c r="AF63" s="1">
-        <v>0</v>
-      </c>
       <c r="AG63" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH63" s="1">
-        <v>0</v>
       </c>
       <c r="AI63" s="1">
         <v>0.1</v>
@@ -9373,8 +8569,8 @@
       </c>
     </row>
     <row r="64" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B64" s="1">
-        <v>60</v>
+      <c r="B64" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>101</v>
@@ -9383,7 +8579,7 @@
         <v>7</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(D64, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G64</f>
@@ -9456,32 +8652,14 @@
       <c r="Y64" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z64" s="1">
-        <v>0</v>
-      </c>
       <c r="AA64" s="1">
         <v>0.3</v>
       </c>
       <c r="AB64" s="1">
         <v>0.25</v>
       </c>
-      <c r="AC64" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD64" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF64" s="1">
-        <v>0</v>
-      </c>
       <c r="AG64" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH64" s="1">
-        <v>0</v>
       </c>
       <c r="AI64" s="1">
         <v>0.1</v>
@@ -9494,8 +8672,8 @@
       </c>
     </row>
     <row r="65" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B65" s="1">
-        <v>61</v>
+      <c r="B65" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>102</v>
@@ -9504,7 +8682,7 @@
         <v>8</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(D65, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G65</f>
@@ -9577,32 +8755,11 @@
       <c r="Y65" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA65" s="1">
-        <v>0</v>
-      </c>
       <c r="AB65" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF65" s="1">
-        <v>0</v>
-      </c>
       <c r="AG65" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH65" s="1">
-        <v>0</v>
       </c>
       <c r="AI65" s="1">
         <v>0.2</v>
@@ -9615,8 +8772,8 @@
       </c>
     </row>
     <row r="66" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B66" s="1">
-        <v>62</v>
+      <c r="B66" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>103</v>
@@ -9625,7 +8782,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(D66, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G66</f>
@@ -9698,43 +8855,25 @@
       <c r="Y66" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="1">
-        <v>0</v>
-      </c>
       <c r="AB66" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AC66" s="1">
-        <v>0</v>
       </c>
       <c r="AD66" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF66" s="1">
-        <v>0</v>
-      </c>
       <c r="AG66" s="1">
         <v>0.1</v>
       </c>
       <c r="AH66" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AI66" s="1">
-        <v>0</v>
       </c>
       <c r="AK66" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="67" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B67" s="1">
-        <v>63</v>
+      <c r="B67" s="1" t="s">
+        <v>387</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>104</v>
@@ -9743,7 +8882,7 @@
         <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(D67, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G67</f>
@@ -9816,35 +8955,14 @@
       <c r="Y67" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z67" s="1">
-        <v>0</v>
-      </c>
       <c r="AA67" s="1">
         <v>0.4</v>
       </c>
-      <c r="AB67" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD67" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF67" s="1">
-        <v>0</v>
-      </c>
       <c r="AG67" s="1">
         <v>0.1</v>
       </c>
       <c r="AH67" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AI67" s="1">
-        <v>0</v>
       </c>
       <c r="AK67" s="1" t="s">
         <v>259</v>
@@ -9854,8 +8972,8 @@
       </c>
     </row>
     <row r="68" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B68" s="1">
-        <v>64</v>
+      <c r="B68" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>105</v>
@@ -9864,7 +8982,7 @@
         <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(D68, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G68</f>
@@ -9937,27 +9055,12 @@
       <c r="Y68" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="1">
-        <v>0</v>
-      </c>
       <c r="AB68" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AC68" s="1">
-        <v>0</v>
       </c>
       <c r="AD68" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF68" s="1">
-        <v>0</v>
-      </c>
       <c r="AG68" s="1">
         <v>0.1</v>
       </c>
@@ -9975,8 +9078,8 @@
       </c>
     </row>
     <row r="69" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B69" s="1">
-        <v>65</v>
+      <c r="B69" s="1" t="s">
+        <v>389</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>106</v>
@@ -9985,7 +9088,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(D69, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G69</f>
@@ -10058,27 +9161,12 @@
       <c r="Y69" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z69" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="1">
-        <v>0</v>
-      </c>
       <c r="AB69" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AC69" s="1">
-        <v>0</v>
       </c>
       <c r="AD69" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE69" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF69" s="1">
-        <v>0</v>
-      </c>
       <c r="AG69" s="1">
         <v>0.1</v>
       </c>
@@ -10096,8 +9184,8 @@
       </c>
     </row>
     <row r="70" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B70" s="1">
-        <v>66</v>
+      <c r="B70" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>107</v>
@@ -10106,7 +9194,7 @@
         <v>7</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(D70, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G70</f>
@@ -10179,33 +9267,15 @@
       <c r="Y70" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z70" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="1">
-        <v>0</v>
-      </c>
       <c r="AB70" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AC70" s="1">
-        <v>0</v>
       </c>
       <c r="AD70" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE70" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF70" s="1">
-        <v>0</v>
-      </c>
       <c r="AG70" s="1">
         <v>0.05</v>
       </c>
-      <c r="AH70" s="1">
-        <v>0</v>
-      </c>
       <c r="AI70" s="1">
         <v>0.1</v>
       </c>
@@ -10217,8 +9287,8 @@
       </c>
     </row>
     <row r="71" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B71" s="1">
-        <v>67</v>
+      <c r="B71" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>108</v>
@@ -10227,7 +9297,7 @@
         <v>8</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(D71, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G71</f>
@@ -10300,27 +9370,12 @@
       <c r="Y71" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="1">
-        <v>0</v>
-      </c>
       <c r="AB71" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AC71" s="1">
-        <v>0</v>
       </c>
       <c r="AD71" s="1">
         <v>0.25</v>
       </c>
-      <c r="AE71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF71" s="1">
-        <v>0</v>
-      </c>
       <c r="AG71" s="1">
         <v>0.1</v>
       </c>
@@ -10338,8 +9393,8 @@
       </c>
     </row>
     <row r="72" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B72" s="1">
-        <v>68</v>
+      <c r="B72" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>109</v>
@@ -10348,7 +9403,7 @@
         <v>7</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(D72, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G72</f>
@@ -10421,30 +9476,15 @@
       <c r="Y72" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z72" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="1">
-        <v>0</v>
-      </c>
       <c r="AB72" s="1">
         <v>0.3</v>
       </c>
-      <c r="AC72" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD72" s="1">
-        <v>0</v>
-      </c>
       <c r="AE72" s="1">
         <v>0.1</v>
       </c>
       <c r="AF72" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG72" s="1">
-        <v>0</v>
-      </c>
       <c r="AH72" s="1">
         <v>0.1</v>
       </c>
@@ -10452,15 +9492,15 @@
         <v>0.1</v>
       </c>
       <c r="AK72" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AL72" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="73" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B73" s="1">
-        <v>69</v>
+      <c r="B73" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>110</v>
@@ -10469,7 +9509,7 @@
         <v>8</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(D73, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G73</f>
@@ -10542,32 +9582,11 @@
       <c r="Y73" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="1">
-        <v>0</v>
-      </c>
       <c r="AB73" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE73" s="1">
-        <v>0</v>
-      </c>
       <c r="AF73" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH73" s="1">
-        <v>0</v>
       </c>
       <c r="AI73" s="1">
         <v>0.1</v>
@@ -10576,12 +9595,12 @@
         <v>263</v>
       </c>
       <c r="AL73" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B74" s="1">
-        <v>70</v>
+      <c r="B74" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>111</v>
@@ -10590,7 +9609,7 @@
         <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(D74, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G74</f>
@@ -10663,32 +9682,11 @@
       <c r="Y74" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z74" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="1">
-        <v>0</v>
-      </c>
       <c r="AB74" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC74" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD74" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE74" s="1">
-        <v>0</v>
-      </c>
       <c r="AF74" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG74" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH74" s="1">
-        <v>0</v>
       </c>
       <c r="AI74" s="1">
         <v>0.1</v>
@@ -10701,8 +9699,8 @@
       </c>
     </row>
     <row r="75" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B75" s="1">
-        <v>71</v>
+      <c r="B75" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>112</v>
@@ -10711,7 +9709,7 @@
         <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(D75, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G75</f>
@@ -10784,29 +9782,11 @@
       <c r="Y75" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="1">
-        <v>0</v>
-      </c>
       <c r="AB75" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE75" s="1">
-        <v>0</v>
-      </c>
       <c r="AF75" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG75" s="1">
-        <v>0</v>
       </c>
       <c r="AH75" s="1">
         <v>0.1</v>
@@ -10822,8 +9802,8 @@
       </c>
     </row>
     <row r="76" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B76" s="1">
-        <v>72</v>
+      <c r="B76" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>113</v>
@@ -10832,7 +9812,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(D76, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G76</f>
@@ -10905,32 +9885,11 @@
       <c r="Y76" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="1">
-        <v>0</v>
-      </c>
       <c r="AB76" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="1">
-        <v>0</v>
-      </c>
       <c r="AF76" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH76" s="1">
-        <v>0</v>
       </c>
       <c r="AI76" s="1">
         <v>0.1</v>
@@ -10943,8 +9902,8 @@
       </c>
     </row>
     <row r="77" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B77" s="1">
-        <v>73</v>
+      <c r="B77" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>114</v>
@@ -10953,7 +9912,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(D77, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G77</f>
@@ -11026,32 +9985,11 @@
       <c r="Y77" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="1">
-        <v>0</v>
-      </c>
       <c r="AB77" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="1">
-        <v>0</v>
-      </c>
       <c r="AF77" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH77" s="1">
-        <v>0</v>
       </c>
       <c r="AI77" s="1">
         <v>0.1</v>
@@ -11061,8 +9999,8 @@
       </c>
     </row>
     <row r="78" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B78" s="1">
-        <v>74</v>
+      <c r="B78" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>115</v>
@@ -11071,7 +10009,7 @@
         <v>4</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(D78, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G78</f>
@@ -11144,32 +10082,11 @@
       <c r="Y78" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="1">
-        <v>0</v>
-      </c>
       <c r="AB78" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="1">
-        <v>0</v>
-      </c>
       <c r="AF78" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH78" s="1">
-        <v>0</v>
       </c>
       <c r="AI78" s="1">
         <v>0.1</v>
@@ -11182,8 +10099,8 @@
       </c>
     </row>
     <row r="79" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B79" s="1">
-        <v>75</v>
+      <c r="B79" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>116</v>
@@ -11192,7 +10109,7 @@
         <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(D79, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G79</f>
@@ -11265,32 +10182,11 @@
       <c r="Y79" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="1">
-        <v>0</v>
-      </c>
       <c r="AB79" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="1">
-        <v>0</v>
-      </c>
       <c r="AF79" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH79" s="1">
-        <v>0</v>
       </c>
       <c r="AI79" s="1">
         <v>0.1</v>
@@ -11303,8 +10199,8 @@
       </c>
     </row>
     <row r="80" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B80" s="1">
-        <v>76</v>
+      <c r="B80" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>117</v>
@@ -11313,7 +10209,7 @@
         <v>6</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(D80, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G80</f>
@@ -11386,32 +10282,11 @@
       <c r="Y80" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="1">
-        <v>0</v>
-      </c>
       <c r="AB80" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="1">
-        <v>0</v>
-      </c>
       <c r="AF80" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="1">
-        <v>0</v>
       </c>
       <c r="AI80" s="1">
         <v>0.1</v>
@@ -11424,8 +10299,8 @@
       </c>
     </row>
     <row r="81" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B81" s="1">
-        <v>77</v>
+      <c r="B81" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>118</v>
@@ -11434,7 +10309,7 @@
         <v>7</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(D81, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G81</f>
@@ -11507,32 +10382,11 @@
       <c r="Y81" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z81" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="1">
-        <v>0</v>
-      </c>
       <c r="AB81" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC81" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD81" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE81" s="1">
-        <v>0</v>
-      </c>
       <c r="AF81" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG81" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH81" s="1">
-        <v>0</v>
       </c>
       <c r="AI81" s="1">
         <v>0.1</v>
@@ -11545,8 +10399,8 @@
       </c>
     </row>
     <row r="82" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B82" s="1">
-        <v>78</v>
+      <c r="B82" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>119</v>
@@ -11555,7 +10409,7 @@
         <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(D82, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G82</f>
@@ -11628,32 +10482,11 @@
       <c r="Y82" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="1">
-        <v>0</v>
-      </c>
       <c r="AB82" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE82" s="1">
-        <v>0</v>
-      </c>
       <c r="AF82" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH82" s="1">
-        <v>0</v>
       </c>
       <c r="AI82" s="1">
         <v>0.2</v>
@@ -11666,8 +10499,8 @@
       </c>
     </row>
     <row r="83" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B83" s="1">
-        <v>79</v>
+      <c r="B83" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>120</v>
@@ -11676,7 +10509,7 @@
         <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(D83, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G83</f>
@@ -11749,32 +10582,11 @@
       <c r="Y83" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="1">
-        <v>0</v>
-      </c>
       <c r="AB83" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="1">
-        <v>0</v>
-      </c>
       <c r="AF83" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH83" s="1">
-        <v>0</v>
       </c>
       <c r="AI83" s="1">
         <v>0.2</v>
@@ -11787,8 +10599,8 @@
       </c>
     </row>
     <row r="84" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B84" s="1">
-        <v>80</v>
+      <c r="B84" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>121</v>
@@ -11797,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(D84, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G84</f>
@@ -11870,32 +10682,11 @@
       <c r="Y84" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="1">
-        <v>0</v>
-      </c>
       <c r="AB84" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE84" s="1">
-        <v>0</v>
-      </c>
       <c r="AF84" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH84" s="1">
-        <v>0</v>
       </c>
       <c r="AI84" s="1">
         <v>0.2</v>
@@ -11908,8 +10699,8 @@
       </c>
     </row>
     <row r="85" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B85" s="1">
-        <v>81</v>
+      <c r="B85" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>122</v>
@@ -11918,7 +10709,7 @@
         <v>8</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(D85, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G85</f>
@@ -11991,32 +10782,11 @@
       <c r="Y85" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z85" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA85" s="1">
-        <v>0</v>
-      </c>
       <c r="AB85" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC85" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD85" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE85" s="1">
-        <v>0</v>
-      </c>
       <c r="AF85" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG85" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH85" s="1">
-        <v>0</v>
       </c>
       <c r="AI85" s="1">
         <v>0.2</v>
@@ -12029,8 +10799,8 @@
       </c>
     </row>
     <row r="86" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B86" s="1">
-        <v>82</v>
+      <c r="B86" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>123</v>
@@ -12039,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F86" s="1">
         <f>VLOOKUP(D86, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G86</f>
@@ -12112,32 +10882,11 @@
       <c r="Y86" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z86" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA86" s="1">
-        <v>0</v>
-      </c>
       <c r="AB86" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC86" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD86" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE86" s="1">
-        <v>0</v>
-      </c>
       <c r="AF86" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG86" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH86" s="1">
-        <v>0</v>
       </c>
       <c r="AI86" s="1">
         <v>0.1</v>
@@ -12150,8 +10899,8 @@
       </c>
     </row>
     <row r="87" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B87" s="1">
-        <v>83</v>
+      <c r="B87" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>124</v>
@@ -12160,7 +10909,7 @@
         <v>3</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F87" s="1">
         <f>VLOOKUP(D87, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G87</f>
@@ -12233,32 +10982,11 @@
       <c r="Y87" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z87" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="1">
-        <v>0</v>
-      </c>
       <c r="AB87" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC87" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD87" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE87" s="1">
-        <v>0</v>
-      </c>
       <c r="AF87" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG87" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH87" s="1">
-        <v>0</v>
       </c>
       <c r="AI87" s="1">
         <v>0.15</v>
@@ -12271,8 +10999,8 @@
       </c>
     </row>
     <row r="88" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B88" s="1">
-        <v>84</v>
+      <c r="B88" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>125</v>
@@ -12281,7 +11009,7 @@
         <v>4</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F88" s="1">
         <f>VLOOKUP(D88, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G88</f>
@@ -12354,32 +11082,11 @@
       <c r="Y88" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA88" s="1">
-        <v>0</v>
-      </c>
       <c r="AB88" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="1">
-        <v>0</v>
-      </c>
       <c r="AF88" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH88" s="1">
-        <v>0</v>
       </c>
       <c r="AI88" s="1">
         <v>0.15</v>
@@ -12392,8 +11099,8 @@
       </c>
     </row>
     <row r="89" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B89" s="1">
-        <v>85</v>
+      <c r="B89" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>126</v>
@@ -12402,7 +11109,7 @@
         <v>5</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F89" s="1">
         <f>VLOOKUP(D89, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G89</f>
@@ -12475,32 +11182,11 @@
       <c r="Y89" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="1">
-        <v>0</v>
-      </c>
       <c r="AB89" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="1">
-        <v>0</v>
-      </c>
       <c r="AF89" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH89" s="1">
-        <v>0</v>
       </c>
       <c r="AI89" s="1">
         <v>0.2</v>
@@ -12513,8 +11199,8 @@
       </c>
     </row>
     <row r="90" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B90" s="1">
-        <v>86</v>
+      <c r="B90" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>127</v>
@@ -12523,7 +11209,7 @@
         <v>6</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F90" s="1">
         <f>VLOOKUP(D90, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G90</f>
@@ -12596,32 +11282,11 @@
       <c r="Y90" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA90" s="1">
-        <v>0</v>
-      </c>
       <c r="AB90" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE90" s="1">
-        <v>0</v>
-      </c>
       <c r="AF90" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH90" s="1">
-        <v>0</v>
       </c>
       <c r="AI90" s="1">
         <v>0.2</v>
@@ -12634,8 +11299,8 @@
       </c>
     </row>
     <row r="91" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B91" s="1">
-        <v>87</v>
+      <c r="B91" s="1" t="s">
+        <v>411</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>128</v>
@@ -12644,7 +11309,7 @@
         <v>7</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F91" s="1">
         <f>VLOOKUP(D91, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G91</f>
@@ -12717,32 +11382,11 @@
       <c r="Y91" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="1">
-        <v>0</v>
-      </c>
       <c r="AB91" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="1">
-        <v>0</v>
-      </c>
       <c r="AF91" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH91" s="1">
-        <v>0</v>
       </c>
       <c r="AI91" s="1">
         <v>0.25</v>
@@ -12755,8 +11399,8 @@
       </c>
     </row>
     <row r="92" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B92" s="1">
-        <v>88</v>
+      <c r="B92" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>129</v>
@@ -12765,7 +11409,7 @@
         <v>4</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F92" s="1">
         <f>VLOOKUP(D92, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G92</f>
@@ -12838,33 +11482,12 @@
       <c r="Y92" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z92" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA92" s="1">
-        <v>0</v>
-      </c>
       <c r="AB92" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC92" s="1">
-        <v>0</v>
-      </c>
       <c r="AD92" s="1">
         <v>0.6</v>
       </c>
-      <c r="AE92" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF92" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG92" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH92" s="1">
-        <v>0</v>
-      </c>
       <c r="AI92" s="1">
         <v>0.05</v>
       </c>
@@ -12873,8 +11496,8 @@
       </c>
     </row>
     <row r="93" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B93" s="1">
-        <v>89</v>
+      <c r="B93" s="1" t="s">
+        <v>413</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>130</v>
@@ -12883,7 +11506,7 @@
         <v>6</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F93" s="1">
         <f>VLOOKUP(D93, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G93</f>
@@ -12956,33 +11579,12 @@
       <c r="Y93" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z93" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="1">
-        <v>0</v>
-      </c>
       <c r="AB93" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC93" s="1">
-        <v>0</v>
-      </c>
       <c r="AD93" s="1">
         <v>0.6</v>
       </c>
-      <c r="AE93" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF93" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG93" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH93" s="1">
-        <v>0</v>
-      </c>
       <c r="AI93" s="1">
         <v>0.05</v>
       </c>
@@ -12994,8 +11596,8 @@
       </c>
     </row>
     <row r="94" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B94" s="1">
-        <v>90</v>
+      <c r="B94" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>131</v>
@@ -13004,7 +11606,7 @@
         <v>2</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F94" s="1">
         <f>VLOOKUP(D94, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G94</f>
@@ -13077,35 +11679,11 @@
       <c r="Y94" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="1">
-        <v>0</v>
-      </c>
       <c r="AB94" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="1">
-        <v>0</v>
-      </c>
       <c r="AF94" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI94" s="1">
-        <v>0</v>
       </c>
       <c r="AK94" s="1" t="s">
         <v>279</v>
@@ -13115,8 +11693,8 @@
       </c>
     </row>
     <row r="95" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B95" s="1">
-        <v>91</v>
+      <c r="B95" s="1" t="s">
+        <v>415</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>132</v>
@@ -13125,7 +11703,7 @@
         <v>3</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F95" s="1">
         <f>VLOOKUP(D95, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G95</f>
@@ -13198,32 +11776,11 @@
       <c r="Y95" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z95" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA95" s="1">
-        <v>0</v>
-      </c>
       <c r="AB95" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC95" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD95" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE95" s="1">
-        <v>0</v>
-      </c>
       <c r="AF95" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG95" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH95" s="1">
-        <v>0</v>
       </c>
       <c r="AI95" s="1">
         <v>0.15</v>
@@ -13236,8 +11793,8 @@
       </c>
     </row>
     <row r="96" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B96" s="1">
-        <v>92</v>
+      <c r="B96" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>133</v>
@@ -13246,7 +11803,7 @@
         <v>4</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F96" s="1">
         <f>VLOOKUP(D96, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G96</f>
@@ -13319,35 +11876,11 @@
       <c r="Y96" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z96" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="1">
-        <v>0</v>
-      </c>
       <c r="AB96" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC96" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="1">
-        <v>0</v>
-      </c>
       <c r="AF96" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG96" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI96" s="1">
-        <v>0</v>
       </c>
       <c r="AK96" s="1" t="s">
         <v>218</v>
@@ -13357,8 +11890,8 @@
       </c>
     </row>
     <row r="97" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B97" s="1">
-        <v>93</v>
+      <c r="B97" s="1" t="s">
+        <v>417</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>134</v>
@@ -13367,7 +11900,7 @@
         <v>5</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F97" s="1">
         <f>VLOOKUP(D97, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G97</f>
@@ -13437,35 +11970,14 @@
       <c r="X97" s="1">
         <v>1</v>
       </c>
-      <c r="Y97" s="1">
-        <v>0</v>
-      </c>
       <c r="Z97" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AA97" s="1">
-        <v>0</v>
       </c>
       <c r="AB97" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC97" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD97" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE97" s="1">
-        <v>0</v>
-      </c>
       <c r="AF97" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG97" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH97" s="1">
-        <v>0</v>
       </c>
       <c r="AI97" s="1">
         <v>0.1</v>
@@ -13475,8 +11987,8 @@
       </c>
     </row>
     <row r="98" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B98" s="1">
-        <v>94</v>
+      <c r="B98" s="1" t="s">
+        <v>418</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>135</v>
@@ -13485,7 +11997,7 @@
         <v>6</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F98" s="1">
         <f>VLOOKUP(D98, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G98</f>
@@ -13558,32 +12070,11 @@
       <c r="Y98" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z98" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA98" s="1">
-        <v>0</v>
-      </c>
       <c r="AB98" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC98" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD98" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE98" s="1">
-        <v>0</v>
-      </c>
       <c r="AF98" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG98" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH98" s="1">
-        <v>0</v>
       </c>
       <c r="AI98" s="1">
         <v>0.1</v>
@@ -13596,8 +12087,8 @@
       </c>
     </row>
     <row r="99" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B99" s="1">
-        <v>95</v>
+      <c r="B99" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>136</v>
@@ -13606,7 +12097,7 @@
         <v>7</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F99" s="1">
         <f>VLOOKUP(D99, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G99</f>
@@ -13679,32 +12170,11 @@
       <c r="Y99" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z99" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA99" s="1">
-        <v>0</v>
-      </c>
       <c r="AB99" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC99" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD99" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE99" s="1">
-        <v>0</v>
-      </c>
       <c r="AF99" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG99" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH99" s="1">
-        <v>0</v>
       </c>
       <c r="AI99" s="1">
         <v>0.15</v>
@@ -13717,8 +12187,8 @@
       </c>
     </row>
     <row r="100" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B100" s="1">
-        <v>96</v>
+      <c r="B100" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>137</v>
@@ -13727,7 +12197,7 @@
         <v>2</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F100" s="1">
         <f>VLOOKUP(D100, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G100</f>
@@ -13800,32 +12270,11 @@
       <c r="Y100" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z100" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="1">
-        <v>0</v>
-      </c>
       <c r="AB100" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC100" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="1">
-        <v>0</v>
-      </c>
       <c r="AF100" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG100" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH100" s="1">
-        <v>0</v>
       </c>
       <c r="AI100" s="1">
         <v>0.05</v>
@@ -13835,8 +12284,8 @@
       </c>
     </row>
     <row r="101" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B101" s="1">
-        <v>97</v>
+      <c r="B101" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>138</v>
@@ -13845,7 +12294,7 @@
         <v>3</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F101" s="1">
         <f>VLOOKUP(D101, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G101</f>
@@ -13918,32 +12367,11 @@
       <c r="Y101" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="1">
-        <v>0</v>
-      </c>
       <c r="AB101" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="1">
-        <v>0</v>
-      </c>
       <c r="AF101" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH101" s="1">
-        <v>0</v>
       </c>
       <c r="AI101" s="1">
         <v>0.05</v>
@@ -13956,8 +12384,8 @@
       </c>
     </row>
     <row r="102" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B102" s="1">
-        <v>98</v>
+      <c r="B102" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>139</v>
@@ -13966,7 +12394,7 @@
         <v>4</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F102" s="1">
         <f>VLOOKUP(D102, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G102</f>
@@ -14039,33 +12467,12 @@
       <c r="Y102" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z102" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="1">
-        <v>0</v>
-      </c>
       <c r="AB102" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC102" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="1">
-        <v>0</v>
-      </c>
       <c r="AF102" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG102" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH102" s="1">
-        <v>0</v>
-      </c>
       <c r="AI102" s="1">
         <v>0.05</v>
       </c>
@@ -14077,8 +12484,8 @@
       </c>
     </row>
     <row r="103" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B103" s="1">
-        <v>99</v>
+      <c r="B103" s="1" t="s">
+        <v>423</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>140</v>
@@ -14087,7 +12494,7 @@
         <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F103" s="1">
         <f>VLOOKUP(D103, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G103</f>
@@ -14160,33 +12567,12 @@
       <c r="Y103" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z103" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA103" s="1">
-        <v>0</v>
-      </c>
       <c r="AB103" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC103" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="1">
-        <v>0</v>
-      </c>
       <c r="AF103" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG103" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH103" s="1">
-        <v>0</v>
-      </c>
       <c r="AI103" s="1">
         <v>0.05</v>
       </c>
@@ -14198,8 +12584,8 @@
       </c>
     </row>
     <row r="104" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B104" s="1">
-        <v>100</v>
+      <c r="B104" s="1" t="s">
+        <v>424</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>141</v>
@@ -14208,7 +12594,7 @@
         <v>6</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F104" s="1">
         <f>VLOOKUP(D104, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G104</f>
@@ -14281,33 +12667,12 @@
       <c r="Y104" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z104" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA104" s="1">
-        <v>0</v>
-      </c>
       <c r="AB104" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC104" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD104" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE104" s="1">
-        <v>0</v>
-      </c>
       <c r="AF104" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG104" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH104" s="1">
-        <v>0</v>
-      </c>
       <c r="AI104" s="1">
         <v>0.05</v>
       </c>
@@ -14319,8 +12684,8 @@
       </c>
     </row>
     <row r="105" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B105" s="1">
-        <v>101</v>
+      <c r="B105" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>142</v>
@@ -14329,7 +12694,7 @@
         <v>7</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F105" s="1">
         <f>VLOOKUP(D105, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G105</f>
@@ -14402,33 +12767,12 @@
       <c r="Y105" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA105" s="1">
-        <v>0</v>
-      </c>
       <c r="AB105" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE105" s="1">
-        <v>0</v>
-      </c>
       <c r="AF105" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH105" s="1">
-        <v>0</v>
-      </c>
       <c r="AI105" s="1">
         <v>0.1</v>
       </c>
@@ -14440,8 +12784,8 @@
       </c>
     </row>
     <row r="106" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B106" s="1">
-        <v>102</v>
+      <c r="B106" s="1" t="s">
+        <v>426</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>143</v>
@@ -14450,7 +12794,7 @@
         <v>7</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F106" s="1">
         <f>VLOOKUP(D106, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G106</f>
@@ -14523,30 +12867,15 @@
       <c r="Y106" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z106" s="1">
-        <v>0</v>
-      </c>
       <c r="AA106" s="1">
         <v>0.2</v>
       </c>
       <c r="AB106" s="1">
         <v>0.2</v>
       </c>
-      <c r="AC106" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD106" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE106" s="1">
-        <v>0</v>
-      </c>
       <c r="AF106" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG106" s="1">
-        <v>0</v>
-      </c>
       <c r="AH106" s="1">
         <v>0.05</v>
       </c>
@@ -14561,8 +12890,8 @@
       </c>
     </row>
     <row r="107" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B107" s="1">
-        <v>103</v>
+      <c r="B107" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>144</v>
@@ -14571,7 +12900,7 @@
         <v>8</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F107" s="1">
         <f>VLOOKUP(D107, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G107</f>
@@ -14644,33 +12973,12 @@
       <c r="Y107" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z107" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA107" s="1">
-        <v>0</v>
-      </c>
       <c r="AB107" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC107" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD107" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE107" s="1">
-        <v>0</v>
-      </c>
       <c r="AF107" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG107" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH107" s="1">
-        <v>0</v>
-      </c>
       <c r="AI107" s="1">
         <v>0.1</v>
       </c>
@@ -14682,8 +12990,8 @@
       </c>
     </row>
     <row r="108" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B108" s="1">
-        <v>104</v>
+      <c r="B108" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>145</v>
@@ -14692,7 +13000,7 @@
         <v>2</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F108" s="1">
         <f>VLOOKUP(D108, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G108</f>
@@ -14765,32 +13073,14 @@
       <c r="Y108" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z108" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA108" s="1">
-        <v>0</v>
-      </c>
       <c r="AB108" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC108" s="1">
-        <v>0</v>
-      </c>
       <c r="AD108" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE108" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF108" s="1">
-        <v>0</v>
-      </c>
       <c r="AG108" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH108" s="1">
-        <v>0</v>
       </c>
       <c r="AI108" s="1">
         <v>0.05</v>
@@ -14800,8 +13090,8 @@
       </c>
     </row>
     <row r="109" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B109" s="1">
-        <v>105</v>
+      <c r="B109" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>146</v>
@@ -14810,7 +13100,7 @@
         <v>3</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F109" s="1">
         <f>VLOOKUP(D109, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G109</f>
@@ -14883,32 +13173,14 @@
       <c r="Y109" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z109" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA109" s="1">
-        <v>0</v>
-      </c>
       <c r="AB109" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC109" s="1">
-        <v>0</v>
-      </c>
       <c r="AD109" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE109" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF109" s="1">
-        <v>0</v>
-      </c>
       <c r="AG109" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH109" s="1">
-        <v>0</v>
       </c>
       <c r="AI109" s="1">
         <v>0.05</v>
@@ -14921,8 +13193,8 @@
       </c>
     </row>
     <row r="110" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B110" s="1">
-        <v>106</v>
+      <c r="B110" s="1" t="s">
+        <v>430</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>147</v>
@@ -14931,7 +13203,7 @@
         <v>4</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F110" s="1">
         <f>VLOOKUP(D110, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G110</f>
@@ -15004,32 +13276,14 @@
       <c r="Y110" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z110" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA110" s="1">
-        <v>0</v>
-      </c>
       <c r="AB110" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC110" s="1">
-        <v>0</v>
-      </c>
       <c r="AD110" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE110" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF110" s="1">
-        <v>0</v>
-      </c>
       <c r="AG110" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH110" s="1">
-        <v>0</v>
       </c>
       <c r="AI110" s="1">
         <v>0.05</v>
@@ -15042,8 +13296,8 @@
       </c>
     </row>
     <row r="111" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B111" s="1">
-        <v>107</v>
+      <c r="B111" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>148</v>
@@ -15052,7 +13306,7 @@
         <v>5</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F111" s="1">
         <f>VLOOKUP(D111, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G111</f>
@@ -15125,32 +13379,14 @@
       <c r="Y111" s="1">
         <v>0.2</v>
       </c>
-      <c r="Z111" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA111" s="1">
-        <v>0</v>
-      </c>
       <c r="AB111" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC111" s="1">
-        <v>0</v>
-      </c>
       <c r="AD111" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE111" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF111" s="1">
-        <v>0</v>
-      </c>
       <c r="AG111" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AH111" s="1">
-        <v>0</v>
       </c>
       <c r="AI111" s="1">
         <v>0.05</v>
@@ -15163,8 +13399,8 @@
       </c>
     </row>
     <row r="112" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B112" s="1">
-        <v>108</v>
+      <c r="B112" s="1" t="s">
+        <v>432</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>149</v>
@@ -15173,7 +13409,7 @@
         <v>2</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F112" s="1">
         <f>VLOOKUP(D112, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G112</f>
@@ -15246,33 +13482,15 @@
       <c r="Y112" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z112" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA112" s="1">
-        <v>0</v>
-      </c>
       <c r="AB112" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC112" s="1">
-        <v>0</v>
-      </c>
       <c r="AD112" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE112" s="1">
-        <v>0</v>
-      </c>
       <c r="AF112" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG112" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH112" s="1">
-        <v>0</v>
-      </c>
       <c r="AI112" s="1">
         <v>0.15</v>
       </c>
@@ -15281,8 +13499,8 @@
       </c>
     </row>
     <row r="113" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B113" s="1">
-        <v>109</v>
+      <c r="B113" s="1" t="s">
+        <v>433</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>150</v>
@@ -15291,7 +13509,7 @@
         <v>3</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F113" s="1">
         <f>VLOOKUP(D113, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G113</f>
@@ -15364,33 +13582,15 @@
       <c r="Y113" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z113" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA113" s="1">
-        <v>0</v>
-      </c>
       <c r="AB113" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC113" s="1">
-        <v>0</v>
-      </c>
       <c r="AD113" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE113" s="1">
-        <v>0</v>
-      </c>
       <c r="AF113" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG113" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH113" s="1">
-        <v>0</v>
-      </c>
       <c r="AI113" s="1">
         <v>0.15</v>
       </c>
@@ -15399,8 +13599,8 @@
       </c>
     </row>
     <row r="114" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B114" s="1">
-        <v>110</v>
+      <c r="B114" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>151</v>
@@ -15409,7 +13609,7 @@
         <v>4</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F114" s="1">
         <f>VLOOKUP(D114, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G114</f>
@@ -15482,33 +13682,15 @@
       <c r="Y114" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="1">
-        <v>0</v>
-      </c>
       <c r="AB114" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC114" s="1">
-        <v>0</v>
-      </c>
       <c r="AD114" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE114" s="1">
-        <v>0</v>
-      </c>
       <c r="AF114" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH114" s="1">
-        <v>0</v>
-      </c>
       <c r="AI114" s="1">
         <v>0.2</v>
       </c>
@@ -15517,8 +13699,8 @@
       </c>
     </row>
     <row r="115" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B115" s="1">
-        <v>111</v>
+      <c r="B115" s="1" t="s">
+        <v>435</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>152</v>
@@ -15527,7 +13709,7 @@
         <v>5</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F115" s="1">
         <f>VLOOKUP(D115, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G115</f>
@@ -15600,33 +13782,15 @@
       <c r="Y115" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z115" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA115" s="1">
-        <v>0</v>
-      </c>
       <c r="AB115" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC115" s="1">
-        <v>0</v>
-      </c>
       <c r="AD115" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE115" s="1">
-        <v>0</v>
-      </c>
       <c r="AF115" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG115" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH115" s="1">
-        <v>0</v>
-      </c>
       <c r="AI115" s="1">
         <v>0.2</v>
       </c>
@@ -15635,8 +13799,8 @@
       </c>
     </row>
     <row r="116" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B116" s="1">
-        <v>112</v>
+      <c r="B116" s="1" t="s">
+        <v>436</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>153</v>
@@ -15645,7 +13809,7 @@
         <v>6</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F116" s="1">
         <f>VLOOKUP(D116, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G116</f>
@@ -15718,33 +13882,15 @@
       <c r="Y116" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z116" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="1">
-        <v>0</v>
-      </c>
       <c r="AB116" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC116" s="1">
-        <v>0</v>
-      </c>
       <c r="AD116" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE116" s="1">
-        <v>0</v>
-      </c>
       <c r="AF116" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG116" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH116" s="1">
-        <v>0</v>
-      </c>
       <c r="AI116" s="1">
         <v>0.25</v>
       </c>
@@ -15753,8 +13899,8 @@
       </c>
     </row>
     <row r="117" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B117" s="1">
-        <v>113</v>
+      <c r="B117" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>154</v>
@@ -15763,7 +13909,7 @@
         <v>7</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F117" s="1">
         <f>VLOOKUP(D117, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G117</f>
@@ -15836,33 +13982,15 @@
       <c r="Y117" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z117" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA117" s="1">
-        <v>0</v>
-      </c>
       <c r="AB117" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC117" s="1">
-        <v>0</v>
-      </c>
       <c r="AD117" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE117" s="1">
-        <v>0</v>
-      </c>
       <c r="AF117" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG117" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH117" s="1">
-        <v>0</v>
-      </c>
       <c r="AI117" s="1">
         <v>0.25</v>
       </c>
@@ -15871,8 +13999,8 @@
       </c>
     </row>
     <row r="118" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B118" s="1">
-        <v>114</v>
+      <c r="B118" s="1" t="s">
+        <v>438</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>155</v>
@@ -15881,7 +14009,7 @@
         <v>8</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F118" s="1">
         <f>VLOOKUP(D118, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G118</f>
@@ -15954,33 +14082,15 @@
       <c r="Y118" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z118" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="1">
-        <v>0</v>
-      </c>
       <c r="AB118" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC118" s="1">
-        <v>0</v>
-      </c>
       <c r="AD118" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE118" s="1">
-        <v>0</v>
-      </c>
       <c r="AF118" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG118" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH118" s="1">
-        <v>0</v>
-      </c>
       <c r="AI118" s="1">
         <v>0.25</v>
       </c>
@@ -15989,8 +14099,8 @@
       </c>
     </row>
     <row r="119" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B119" s="1">
-        <v>115</v>
+      <c r="B119" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>156</v>
@@ -15999,7 +14109,7 @@
         <v>9</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F119" s="1">
         <f>VLOOKUP(D119, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G119</f>
@@ -16072,33 +14182,15 @@
       <c r="Y119" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="1">
-        <v>0</v>
-      </c>
       <c r="AB119" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC119" s="1">
-        <v>0</v>
-      </c>
       <c r="AD119" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE119" s="1">
-        <v>0</v>
-      </c>
       <c r="AF119" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH119" s="1">
-        <v>0</v>
-      </c>
       <c r="AI119" s="1">
         <v>0.3</v>
       </c>
@@ -16107,8 +14199,8 @@
       </c>
     </row>
     <row r="120" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B120" s="1">
-        <v>116</v>
+      <c r="B120" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>157</v>
@@ -16117,7 +14209,7 @@
         <v>3</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F120" s="1">
         <f>VLOOKUP(D120, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G120</f>
@@ -16190,36 +14282,12 @@
       <c r="Y120" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z120" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA120" s="1">
-        <v>0</v>
-      </c>
       <c r="AB120" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC120" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD120" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE120" s="1">
-        <v>0</v>
-      </c>
       <c r="AF120" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG120" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH120" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI120" s="1">
-        <v>0</v>
-      </c>
       <c r="AK120" s="1" t="s">
         <v>288</v>
       </c>
@@ -16228,8 +14296,8 @@
       </c>
     </row>
     <row r="121" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B121" s="1">
-        <v>117</v>
+      <c r="B121" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>158</v>
@@ -16238,7 +14306,7 @@
         <v>4</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F121" s="1">
         <f>VLOOKUP(D121, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G121</f>
@@ -16311,30 +14379,15 @@
       <c r="Y121" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z121" s="1">
-        <v>0</v>
-      </c>
       <c r="AA121" s="1">
         <v>0.3</v>
       </c>
       <c r="AB121" s="1">
         <v>0.15</v>
       </c>
-      <c r="AC121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE121" s="1">
-        <v>0</v>
-      </c>
       <c r="AF121" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG121" s="1">
-        <v>0</v>
-      </c>
       <c r="AH121" s="1">
         <v>0.1</v>
       </c>
@@ -16349,8 +14402,8 @@
       </c>
     </row>
     <row r="122" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B122" s="1">
-        <v>118</v>
+      <c r="B122" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>159</v>
@@ -16359,7 +14412,7 @@
         <v>5</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F122" s="1">
         <f>VLOOKUP(D122, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G122</f>
@@ -16432,33 +14485,12 @@
       <c r="Y122" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA122" s="1">
-        <v>0</v>
-      </c>
       <c r="AB122" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="1">
-        <v>0</v>
-      </c>
       <c r="AF122" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH122" s="1">
-        <v>0</v>
-      </c>
       <c r="AI122" s="1">
         <v>0.05</v>
       </c>
@@ -16470,8 +14502,8 @@
       </c>
     </row>
     <row r="123" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B123" s="1">
-        <v>119</v>
+      <c r="B123" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>160</v>
@@ -16480,7 +14512,7 @@
         <v>6</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F123" s="1">
         <f>VLOOKUP(D123, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G123</f>
@@ -16553,33 +14585,12 @@
       <c r="Y123" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA123" s="1">
-        <v>0</v>
-      </c>
       <c r="AB123" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE123" s="1">
-        <v>0</v>
-      </c>
       <c r="AF123" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH123" s="1">
-        <v>0</v>
-      </c>
       <c r="AI123" s="1">
         <v>0.1</v>
       </c>
@@ -16591,8 +14602,8 @@
       </c>
     </row>
     <row r="124" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B124" s="1">
-        <v>120</v>
+      <c r="B124" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>161</v>
@@ -16601,7 +14612,7 @@
         <v>7</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F124" s="1">
         <f>VLOOKUP(D124, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G124</f>
@@ -16674,33 +14685,12 @@
       <c r="Y124" s="1">
         <v>0.2</v>
       </c>
-      <c r="Z124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA124" s="1">
-        <v>0</v>
-      </c>
       <c r="AB124" s="1">
         <v>0.5</v>
       </c>
-      <c r="AC124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE124" s="1">
-        <v>0</v>
-      </c>
       <c r="AF124" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH124" s="1">
-        <v>0</v>
-      </c>
       <c r="AI124" s="1">
         <v>0.15</v>
       </c>
@@ -16712,8 +14702,8 @@
       </c>
     </row>
     <row r="125" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B125" s="1">
-        <v>121</v>
+      <c r="B125" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>162</v>
@@ -16722,7 +14712,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F125" s="1">
         <f>VLOOKUP(D125, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G125</f>
@@ -16795,32 +14785,11 @@
       <c r="Y125" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA125" s="1">
-        <v>0</v>
-      </c>
       <c r="AB125" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE125" s="1">
-        <v>0</v>
-      </c>
       <c r="AF125" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH125" s="1">
-        <v>0</v>
       </c>
       <c r="AI125" s="1">
         <v>0.05</v>
@@ -16833,8 +14802,8 @@
       </c>
     </row>
     <row r="126" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B126" s="1">
-        <v>122</v>
+      <c r="B126" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>163</v>
@@ -16843,7 +14812,7 @@
         <v>3</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F126" s="1">
         <f>VLOOKUP(D126, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G126</f>
@@ -16916,32 +14885,11 @@
       <c r="Y126" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA126" s="1">
-        <v>0</v>
-      </c>
       <c r="AB126" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE126" s="1">
-        <v>0</v>
-      </c>
       <c r="AF126" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH126" s="1">
-        <v>0</v>
       </c>
       <c r="AI126" s="1">
         <v>0.15</v>
@@ -16954,8 +14902,8 @@
       </c>
     </row>
     <row r="127" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B127" s="1">
-        <v>123</v>
+      <c r="B127" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>164</v>
@@ -16964,7 +14912,7 @@
         <v>4</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F127" s="1">
         <f>VLOOKUP(D127, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G127</f>
@@ -17037,32 +14985,11 @@
       <c r="Y127" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z127" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA127" s="1">
-        <v>0</v>
-      </c>
       <c r="AB127" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC127" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD127" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE127" s="1">
-        <v>0</v>
-      </c>
       <c r="AF127" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG127" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH127" s="1">
-        <v>0</v>
       </c>
       <c r="AI127" s="1">
         <v>0.2</v>
@@ -17072,8 +14999,8 @@
       </c>
     </row>
     <row r="128" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B128" s="1">
-        <v>124</v>
+      <c r="B128" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>165</v>
@@ -17082,7 +15009,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F128" s="1">
         <f>VLOOKUP(D128, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G128</f>
@@ -17155,32 +15082,11 @@
       <c r="Y128" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z128" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="1">
-        <v>0</v>
-      </c>
       <c r="AB128" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC128" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD128" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE128" s="1">
-        <v>0</v>
-      </c>
       <c r="AF128" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG128" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH128" s="1">
-        <v>0</v>
       </c>
       <c r="AI128" s="1">
         <v>0.2</v>
@@ -17193,8 +15099,8 @@
       </c>
     </row>
     <row r="129" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B129" s="1">
-        <v>125</v>
+      <c r="B129" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>166</v>
@@ -17203,7 +15109,7 @@
         <v>6</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F129" s="1">
         <f>VLOOKUP(D129, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G129</f>
@@ -17273,39 +15179,9 @@
       <c r="X129" s="1">
         <v>0.9</v>
       </c>
-      <c r="Y129" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB129" s="1">
-        <v>0</v>
-      </c>
       <c r="AC129" s="1">
         <v>0.9</v>
       </c>
-      <c r="AD129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI129" s="1">
-        <v>0</v>
-      </c>
       <c r="AK129" s="1" t="s">
         <v>291</v>
       </c>
@@ -17314,8 +15190,8 @@
       </c>
     </row>
     <row r="130" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B130" s="1">
-        <v>126</v>
+      <c r="B130" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>167</v>
@@ -17324,7 +15200,7 @@
         <v>3</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F130" s="1">
         <f>VLOOKUP(D130, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G130</f>
@@ -17397,32 +15273,11 @@
       <c r="Y130" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z130" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="1">
-        <v>0</v>
-      </c>
       <c r="AB130" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC130" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD130" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE130" s="1">
-        <v>0</v>
-      </c>
       <c r="AF130" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG130" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH130" s="1">
-        <v>0</v>
       </c>
       <c r="AI130" s="1">
         <v>0.05</v>
@@ -17435,8 +15290,8 @@
       </c>
     </row>
     <row r="131" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B131" s="1">
-        <v>127</v>
+      <c r="B131" s="1" t="s">
+        <v>451</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>168</v>
@@ -17445,7 +15300,7 @@
         <v>4</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F131" s="1">
         <f>VLOOKUP(D131, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G131</f>
@@ -17518,32 +15373,11 @@
       <c r="Y131" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z131" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA131" s="1">
-        <v>0</v>
-      </c>
       <c r="AB131" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC131" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD131" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE131" s="1">
-        <v>0</v>
-      </c>
       <c r="AF131" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG131" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH131" s="1">
-        <v>0</v>
       </c>
       <c r="AI131" s="1">
         <v>0.05</v>
@@ -17556,8 +15390,8 @@
       </c>
     </row>
     <row r="132" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B132" s="1">
-        <v>128</v>
+      <c r="B132" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>169</v>
@@ -17566,7 +15400,7 @@
         <v>5</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F132" s="1">
         <f>VLOOKUP(D132, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G132</f>
@@ -17639,32 +15473,11 @@
       <c r="Y132" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA132" s="1">
-        <v>0</v>
-      </c>
       <c r="AB132" s="1">
         <v>0.45</v>
       </c>
-      <c r="AC132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE132" s="1">
-        <v>0</v>
-      </c>
       <c r="AF132" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH132" s="1">
-        <v>0</v>
       </c>
       <c r="AI132" s="1">
         <v>0.2</v>
@@ -17677,8 +15490,8 @@
       </c>
     </row>
     <row r="133" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B133" s="1">
-        <v>129</v>
+      <c r="B133" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>170</v>
@@ -17687,7 +15500,7 @@
         <v>2</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F133" s="1">
         <f>VLOOKUP(D133, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G133</f>
@@ -17757,46 +15570,16 @@
       <c r="X133" s="1">
         <v>0.9</v>
       </c>
-      <c r="Y133" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z133" s="1">
-        <v>0</v>
-      </c>
       <c r="AA133" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI133" s="1">
-        <v>0</v>
-      </c>
       <c r="AK133" s="1" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="134" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B134" s="1">
-        <v>130</v>
+      <c r="B134" s="1" t="s">
+        <v>454</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>171</v>
@@ -17805,7 +15588,7 @@
         <v>3</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F134" s="1">
         <f>VLOOKUP(D134, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G134</f>
@@ -17875,36 +15658,9 @@
       <c r="X134" s="1">
         <v>0.9</v>
       </c>
-      <c r="Y134" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z134" s="1">
-        <v>0</v>
-      </c>
       <c r="AA134" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH134" s="1">
-        <v>0</v>
-      </c>
       <c r="AI134" s="1">
         <v>0.05</v>
       </c>
@@ -17913,8 +15669,8 @@
       </c>
     </row>
     <row r="135" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B135" s="1">
-        <v>131</v>
+      <c r="B135" s="1" t="s">
+        <v>455</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>172</v>
@@ -17923,7 +15679,7 @@
         <v>4</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F135" s="1">
         <f>VLOOKUP(D135, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G135</f>
@@ -17993,36 +15749,9 @@
       <c r="X135" s="1">
         <v>1</v>
       </c>
-      <c r="Y135" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z135" s="1">
-        <v>0</v>
-      </c>
       <c r="AA135" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH135" s="1">
-        <v>0</v>
-      </c>
       <c r="AI135" s="1">
         <v>0.05</v>
       </c>
@@ -18034,8 +15763,8 @@
       </c>
     </row>
     <row r="136" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B136" s="1">
-        <v>132</v>
+      <c r="B136" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>173</v>
@@ -18044,7 +15773,7 @@
         <v>5</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F136" s="1">
         <f>VLOOKUP(D136, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G136</f>
@@ -18114,36 +15843,9 @@
       <c r="X136" s="1">
         <v>1</v>
       </c>
-      <c r="Y136" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="1">
-        <v>0</v>
-      </c>
       <c r="AA136" s="1">
         <v>0.5</v>
       </c>
-      <c r="AB136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH136" s="1">
-        <v>0</v>
-      </c>
       <c r="AI136" s="1">
         <v>0.05</v>
       </c>
@@ -18155,8 +15857,8 @@
       </c>
     </row>
     <row r="137" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B137" s="1">
-        <v>133</v>
+      <c r="B137" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>174</v>
@@ -18165,7 +15867,7 @@
         <v>6</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F137" s="1">
         <f>VLOOKUP(D137, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G137</f>
@@ -18235,36 +15937,9 @@
       <c r="X137" s="1">
         <v>2</v>
       </c>
-      <c r="Y137" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z137" s="1">
-        <v>0</v>
-      </c>
       <c r="AA137" s="1">
         <v>0.8</v>
       </c>
-      <c r="AB137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH137" s="1">
-        <v>0</v>
-      </c>
       <c r="AI137" s="1">
         <v>0.05</v>
       </c>
@@ -18273,8 +15948,8 @@
       </c>
     </row>
     <row r="138" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B138" s="1">
-        <v>134</v>
+      <c r="B138" s="1" t="s">
+        <v>458</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>175</v>
@@ -18283,7 +15958,7 @@
         <v>7</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F138" s="1">
         <f>VLOOKUP(D138, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G138</f>
@@ -18356,33 +16031,15 @@
       <c r="Y138" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z138" s="1">
-        <v>0</v>
-      </c>
       <c r="AA138" s="1">
         <v>0.2</v>
       </c>
-      <c r="AB138" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC138" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD138" s="1">
-        <v>0</v>
-      </c>
       <c r="AE138" s="1">
         <v>0.35</v>
       </c>
       <c r="AF138" s="1">
         <v>0.1</v>
       </c>
-      <c r="AG138" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH138" s="1">
-        <v>0</v>
-      </c>
       <c r="AI138" s="1">
         <v>0.05</v>
       </c>
@@ -18394,8 +16051,8 @@
       </c>
     </row>
     <row r="139" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B139" s="1">
-        <v>135</v>
+      <c r="B139" s="1" t="s">
+        <v>459</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>176</v>
@@ -18404,7 +16061,7 @@
         <v>3</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F139" s="1">
         <f>VLOOKUP(D139, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G139</f>
@@ -18477,35 +16134,14 @@
       <c r="Y139" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z139" s="1">
-        <v>0</v>
-      </c>
       <c r="AA139" s="1">
         <v>0.2</v>
       </c>
-      <c r="AB139" s="1">
-        <v>0</v>
-      </c>
       <c r="AC139" s="1">
         <v>0.25</v>
       </c>
-      <c r="AD139" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE139" s="1">
-        <v>0</v>
-      </c>
       <c r="AF139" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG139" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH139" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI139" s="1">
-        <v>0</v>
       </c>
       <c r="AK139" s="1" t="s">
         <v>293</v>
@@ -18515,8 +16151,8 @@
       </c>
     </row>
     <row r="140" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B140" s="1">
-        <v>136</v>
+      <c r="B140" s="1" t="s">
+        <v>460</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>177</v>
@@ -18525,7 +16161,7 @@
         <v>6</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F140" s="1">
         <f>VLOOKUP(D140, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G140</f>
@@ -18598,32 +16234,14 @@
       <c r="Y140" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z140" s="1">
-        <v>0</v>
-      </c>
       <c r="AA140" s="1">
         <v>0.2</v>
       </c>
-      <c r="AB140" s="1">
-        <v>0</v>
-      </c>
       <c r="AC140" s="1">
         <v>0.25</v>
       </c>
-      <c r="AD140" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE140" s="1">
-        <v>0</v>
-      </c>
       <c r="AF140" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG140" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH140" s="1">
-        <v>0</v>
       </c>
       <c r="AI140" s="1">
         <v>0.1</v>
@@ -18636,8 +16254,8 @@
       </c>
     </row>
     <row r="141" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B141" s="1">
-        <v>137</v>
+      <c r="B141" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>178</v>
@@ -18646,7 +16264,7 @@
         <v>1</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F141" s="1">
         <f>VLOOKUP(D141, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G141</f>
@@ -18719,32 +16337,11 @@
       <c r="Y141" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z141" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA141" s="1">
-        <v>0</v>
-      </c>
       <c r="AB141" s="1">
         <v>0.3</v>
       </c>
-      <c r="AC141" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD141" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE141" s="1">
-        <v>0</v>
-      </c>
       <c r="AF141" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG141" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH141" s="1">
-        <v>0</v>
       </c>
       <c r="AI141" s="1">
         <v>0.05</v>
@@ -18754,8 +16351,8 @@
       </c>
     </row>
     <row r="142" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B142" s="1">
-        <v>138</v>
+      <c r="B142" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>179</v>
@@ -18764,7 +16361,7 @@
         <v>2</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F142" s="1">
         <f>VLOOKUP(D142, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G142</f>
@@ -18837,32 +16434,11 @@
       <c r="Y142" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z142" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA142" s="1">
-        <v>0</v>
-      </c>
       <c r="AB142" s="1">
         <v>0.3</v>
       </c>
-      <c r="AC142" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD142" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE142" s="1">
-        <v>0</v>
-      </c>
       <c r="AF142" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG142" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH142" s="1">
-        <v>0</v>
       </c>
       <c r="AI142" s="1">
         <v>0.1</v>
@@ -18875,8 +16451,8 @@
       </c>
     </row>
     <row r="143" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B143" s="1">
-        <v>139</v>
+      <c r="B143" s="1" t="s">
+        <v>463</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>180</v>
@@ -18885,7 +16461,7 @@
         <v>3</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F143" s="1">
         <f>VLOOKUP(D143, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G143</f>
@@ -18958,32 +16534,11 @@
       <c r="Y143" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z143" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA143" s="1">
-        <v>0</v>
-      </c>
       <c r="AB143" s="1">
         <v>0.3</v>
       </c>
-      <c r="AC143" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD143" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE143" s="1">
-        <v>0</v>
-      </c>
       <c r="AF143" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG143" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH143" s="1">
-        <v>0</v>
       </c>
       <c r="AI143" s="1">
         <v>0.15</v>
@@ -18996,8 +16551,8 @@
       </c>
     </row>
     <row r="144" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B144" s="1">
-        <v>140</v>
+      <c r="B144" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>181</v>
@@ -19006,7 +16561,7 @@
         <v>4</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F144" s="1">
         <f>VLOOKUP(D144, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G144</f>
@@ -19079,32 +16634,11 @@
       <c r="Y144" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z144" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="1">
-        <v>0</v>
-      </c>
       <c r="AB144" s="1">
         <v>0.3</v>
       </c>
-      <c r="AC144" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD144" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE144" s="1">
-        <v>0</v>
-      </c>
       <c r="AF144" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG144" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH144" s="1">
-        <v>0</v>
       </c>
       <c r="AI144" s="1">
         <v>0.1</v>
@@ -19117,8 +16651,8 @@
       </c>
     </row>
     <row r="145" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="B145" s="1">
-        <v>141</v>
+      <c r="B145" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>182</v>
@@ -19127,7 +16661,7 @@
         <v>9</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F145" s="1">
         <f>VLOOKUP(D145, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G145</f>
@@ -19200,35 +16734,14 @@
       <c r="Y145" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z145" s="1">
-        <v>0</v>
-      </c>
       <c r="AA145" s="1">
         <v>0.4</v>
       </c>
-      <c r="AB145" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC145" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD145" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE145" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF145" s="1">
-        <v>0</v>
-      </c>
       <c r="AG145" s="1">
         <v>0.1</v>
       </c>
       <c r="AH145" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AI145" s="1">
-        <v>0</v>
       </c>
       <c r="AK145" s="1" t="s">
         <v>259</v>
@@ -19250,8 +16763,8 @@
       </c>
     </row>
     <row r="146" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="B146" s="1">
-        <v>142</v>
+      <c r="B146" s="1" t="s">
+        <v>466</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>183</v>
@@ -19260,7 +16773,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F146" s="1">
         <f>VLOOKUP(D146, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G146</f>
@@ -19333,32 +16846,11 @@
       <c r="Y146" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z146" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="1">
-        <v>0</v>
-      </c>
       <c r="AB146" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC146" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD146" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE146" s="1">
-        <v>0</v>
-      </c>
       <c r="AF146" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG146" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH146" s="1">
-        <v>0</v>
       </c>
       <c r="AI146" s="1">
         <v>0.3</v>
@@ -19383,8 +16875,8 @@
       </c>
     </row>
     <row r="147" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="B147" s="1">
-        <v>143</v>
+      <c r="B147" s="1" t="s">
+        <v>467</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>184</v>
@@ -19393,7 +16885,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F147" s="1">
         <f>VLOOKUP(D147, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G147</f>
@@ -19466,33 +16958,15 @@
       <c r="Y147" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z147" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA147" s="1">
-        <v>0</v>
-      </c>
       <c r="AB147" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC147" s="1">
-        <v>0</v>
-      </c>
       <c r="AD147" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE147" s="1">
-        <v>0</v>
-      </c>
       <c r="AF147" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG147" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH147" s="1">
-        <v>0</v>
-      </c>
       <c r="AI147" s="1">
         <v>0.3</v>
       </c>
@@ -19525,8 +16999,8 @@
       </c>
     </row>
     <row r="148" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="B148" s="1">
-        <v>144</v>
+      <c r="B148" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>185</v>
@@ -19535,7 +17009,7 @@
         <v>9</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F148" s="1">
         <f>VLOOKUP(D148, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G148</f>
@@ -19608,33 +17082,15 @@
       <c r="Y148" s="1">
         <v>0.1</v>
       </c>
-      <c r="Z148" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA148" s="1">
-        <v>0</v>
-      </c>
       <c r="AB148" s="1">
         <v>0.05</v>
       </c>
-      <c r="AC148" s="1">
-        <v>0</v>
-      </c>
       <c r="AD148" s="1">
         <v>0.3</v>
       </c>
-      <c r="AE148" s="1">
-        <v>0</v>
-      </c>
       <c r="AF148" s="1">
         <v>0.15</v>
       </c>
-      <c r="AG148" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH148" s="1">
-        <v>0</v>
-      </c>
       <c r="AI148" s="1">
         <v>0.3</v>
       </c>
@@ -19655,8 +17111,8 @@
       </c>
     </row>
     <row r="149" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="B149" s="1">
-        <v>145</v>
+      <c r="B149" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>186</v>
@@ -19665,7 +17121,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F149" s="1">
         <f>VLOOKUP(D149, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G149</f>
@@ -19738,32 +17194,11 @@
       <c r="Y149" s="1">
         <v>0.15</v>
       </c>
-      <c r="Z149" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA149" s="1">
-        <v>0</v>
-      </c>
       <c r="AB149" s="1">
         <v>0.4</v>
       </c>
-      <c r="AC149" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD149" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE149" s="1">
-        <v>0</v>
-      </c>
       <c r="AF149" s="1">
         <v>0.1</v>
-      </c>
-      <c r="AG149" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH149" s="1">
-        <v>0</v>
       </c>
       <c r="AI149" s="1">
         <v>0.35</v>
@@ -19795,7 +17230,7 @@
     <mergeCell ref="AK1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A5:H34 Y5:XFD34 I5:X149 H6:H149 B7:B149 F35:H149">
+  <conditionalFormatting sqref="A5:H34 Y5:XFD34 I5:X149 H6:H149 F35:H149 A5:A149 B6:B149">
     <cfRule type="expression" priority="5">
       <formula xml:space="preserve"> MOD(ROW(),2)</formula>
     </cfRule>

--- a/design/MiniTemplate/Excels/#role.xlsx
+++ b/design/MiniTemplate/Excels/#role.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BiliBili\Work\slime\design\MiniTemplate\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55AD3FA-B7CF-4B58-AEE2-BDBEB38CF841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3563CC-47BC-41A4-8F74-89DFC0480BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -119,10 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ralations</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>list,string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1478,6 +1474,10 @@
   </si>
   <si>
     <t>h145</t>
+  </si>
+  <si>
+    <t>relations</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2398,61 +2398,61 @@
         <v>24</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="V1" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y1" s="10" t="s">
-        <v>29</v>
+        <v>469</v>
       </c>
       <c r="Z1" s="11"/>
       <c r="AA1" s="11"/>
@@ -2481,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -2490,43 +2490,43 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="K2" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y2" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Z2" s="14"/>
       <c r="AA2" s="14"/>
@@ -2539,7 +2539,7 @@
       <c r="AH2" s="14"/>
       <c r="AI2" s="15"/>
       <c r="AK2" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL2" s="14"/>
       <c r="AM2" s="14"/>
@@ -2552,40 +2552,40 @@
     </row>
     <row r="3" spans="1:45" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AB3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AC3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AD3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AD3" s="6" t="s">
+      <c r="AE3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="6" t="s">
+      <c r="AF3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AG3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AG3" s="6" t="s">
+      <c r="AH3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AH3" s="6" t="s">
+      <c r="AI3" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="AI3" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="AK3" s="5">
         <v>1</v>
@@ -2635,58 +2635,58 @@
         <v>9</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="P4" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="R4" s="9" t="s">
+      <c r="T4" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="V4" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="S4" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="V4" s="9" t="s">
+      <c r="W4" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="W4" s="9" t="s">
+      <c r="X4" s="9" t="s">
         <v>216</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>217</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>10</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>23</v>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(D5, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G5</f>
@@ -2804,21 +2804,21 @@
         <v>1</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(D6, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G6</f>
@@ -2895,21 +2895,21 @@
         <v>0.5</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(D7, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G7</f>
@@ -2986,21 +2986,21 @@
         <v>0.5</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(D8, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G8</f>
@@ -3077,21 +3077,21 @@
         <v>0.6</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(D9, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G9</f>
@@ -3171,21 +3171,21 @@
         <v>0.1</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(D10, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G10</f>
@@ -3268,24 +3268,24 @@
         <v>0.1</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1">
         <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(D11, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G11</f>
@@ -3368,24 +3368,24 @@
         <v>0.1</v>
       </c>
       <c r="AK11" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AL11" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="AL11" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1">
         <v>7</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(D12, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G12</f>
@@ -3471,24 +3471,24 @@
         <v>0.1</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(D13, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G13</f>
@@ -3577,24 +3577,24 @@
         <v>0.1</v>
       </c>
       <c r="AK13" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AL13" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="AL13" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1">
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(D14, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G14</f>
@@ -3680,24 +3680,24 @@
         <v>0.1</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1">
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(D15, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G15</f>
@@ -3783,24 +3783,24 @@
         <v>0.2</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1">
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(D16, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G16</f>
@@ -3886,24 +3886,24 @@
         <v>0.1</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(D17, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G17</f>
@@ -3983,21 +3983,21 @@
         <v>0.1</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(D18, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G18</f>
@@ -4077,21 +4077,21 @@
         <v>0.1</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(D19, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G19</f>
@@ -4171,21 +4171,21 @@
         <v>0.1</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(D20, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G20</f>
@@ -4268,24 +4268,24 @@
         <v>0.1</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(D21, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G21</f>
@@ -4368,24 +4368,24 @@
         <v>0.1</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1">
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(D22, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G22</f>
@@ -4465,24 +4465,24 @@
         <v>0.1</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL22" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(D23, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G23</f>
@@ -4562,24 +4562,24 @@
         <v>0.1</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL23" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(D24, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G24</f>
@@ -4659,21 +4659,21 @@
         <v>0.1</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(D25, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G25</f>
@@ -4753,24 +4753,24 @@
         <v>0.1</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D26" s="1">
         <v>6</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(D26, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G26</f>
@@ -4850,21 +4850,21 @@
         <v>0.1</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D27" s="1">
         <v>6</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(D27, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G27</f>
@@ -4944,24 +4944,24 @@
         <v>0.1</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D28" s="1">
         <v>7</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(D28, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G28</f>
@@ -5044,24 +5044,24 @@
         <v>0.1</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D29" s="1">
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(D29, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G29</f>
@@ -5144,24 +5144,24 @@
         <v>0.1</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL29" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D30" s="1">
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(D30, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G30</f>
@@ -5244,24 +5244,24 @@
         <v>0.1</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL30" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D31" s="1">
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(D31, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G31</f>
@@ -5344,24 +5344,24 @@
         <v>0.2</v>
       </c>
       <c r="AK31" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL31" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" s="1">
         <v>2</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(D32, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G32</f>
@@ -5441,21 +5441,21 @@
         <v>0.15</v>
       </c>
       <c r="AK32" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(D33, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G33</f>
@@ -5535,24 +5535,24 @@
         <v>0.15</v>
       </c>
       <c r="AK33" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AL33" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="AL33" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="34" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D34" s="1">
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(D34, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G34</f>
@@ -5632,24 +5632,24 @@
         <v>0.2</v>
       </c>
       <c r="AK34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AL34" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="AL34" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="35" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="1">
         <v>5</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(D35, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G35</f>
@@ -5729,24 +5729,24 @@
         <v>0.2</v>
       </c>
       <c r="AK35" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AL35" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="AL35" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="36" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D36" s="1">
         <v>6</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(D36, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G36</f>
@@ -5829,24 +5829,24 @@
         <v>0.15</v>
       </c>
       <c r="AK36" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL36" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="1">
         <v>7</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(D37, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G37</f>
@@ -5929,24 +5929,24 @@
         <v>0.2</v>
       </c>
       <c r="AK37" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AL37" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="AL37" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="38" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D38" s="1">
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(D38, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G38</f>
@@ -6032,24 +6032,24 @@
         <v>0.1</v>
       </c>
       <c r="AK38" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL38" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D39" s="1">
         <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(D39, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G39</f>
@@ -6132,24 +6132,24 @@
         <v>0.2</v>
       </c>
       <c r="AK39" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL39" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(D40, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G40</f>
@@ -6232,21 +6232,21 @@
         <v>0.1</v>
       </c>
       <c r="AK40" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(D41, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G41</f>
@@ -6329,21 +6329,21 @@
         <v>0.1</v>
       </c>
       <c r="AK41" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="42" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D42" s="1">
         <v>3</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(D42, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G42</f>
@@ -6426,21 +6426,21 @@
         <v>0.1</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D43" s="1">
         <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(D43, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G43</f>
@@ -6526,24 +6526,24 @@
         <v>0.05</v>
       </c>
       <c r="AK43" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL43" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D44" s="1">
         <v>5</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(D44, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G44</f>
@@ -6629,24 +6629,24 @@
         <v>0.1</v>
       </c>
       <c r="AK44" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL44" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D45" s="1">
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(D45, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G45</f>
@@ -6735,24 +6735,24 @@
         <v>0.1</v>
       </c>
       <c r="AK45" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AL45" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D46" s="1">
         <v>7</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(D46, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G46</f>
@@ -6841,24 +6841,24 @@
         <v>0.1</v>
       </c>
       <c r="AK46" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AL46" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D47" s="1">
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(D47, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G47</f>
@@ -6944,24 +6944,24 @@
         <v>0.1</v>
       </c>
       <c r="AK47" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL47" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="AL47" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="48" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D48" s="1">
         <v>9</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(D48, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G48</f>
@@ -7050,24 +7050,24 @@
         <v>0.1</v>
       </c>
       <c r="AK48" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AL48" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(D49, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G49</f>
@@ -7150,21 +7150,21 @@
         <v>0.1</v>
       </c>
       <c r="AK49" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D50" s="1">
         <v>3</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(D50, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G50</f>
@@ -7247,24 +7247,24 @@
         <v>0.2</v>
       </c>
       <c r="AK50" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AL50" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="AL50" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="51" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" s="1">
         <v>4</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(D51, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G51</f>
@@ -7347,24 +7347,24 @@
         <v>0.2</v>
       </c>
       <c r="AK51" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AL51" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D52" s="1">
         <v>5</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(D52, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G52</f>
@@ -7450,24 +7450,24 @@
         <v>0.2</v>
       </c>
       <c r="AK52" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL52" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D53" s="1">
         <v>6</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(D53, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G53</f>
@@ -7553,21 +7553,21 @@
         <v>0.1</v>
       </c>
       <c r="AK53" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D54" s="1">
         <v>7</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(D54, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G54</f>
@@ -7653,24 +7653,24 @@
         <v>0.2</v>
       </c>
       <c r="AK54" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL54" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D55" s="1">
         <v>8</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(D55, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G55</f>
@@ -7756,24 +7756,24 @@
         <v>0.2</v>
       </c>
       <c r="AK55" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AL55" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="AL55" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="56" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D56" s="1">
         <v>9</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(D56, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G56</f>
@@ -7859,24 +7859,24 @@
         <v>0.2</v>
       </c>
       <c r="AK56" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL56" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(D57, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G57</f>
@@ -7956,24 +7956,24 @@
         <v>0.1</v>
       </c>
       <c r="AK57" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AL57" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="58" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D58" s="1">
         <v>5</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(D58, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G58</f>
@@ -8056,24 +8056,24 @@
         <v>0.1</v>
       </c>
       <c r="AK58" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AL58" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="59" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D59" s="1">
         <v>2</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(D59, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G59</f>
@@ -8156,21 +8156,21 @@
         <v>0.1</v>
       </c>
       <c r="AK59" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D60" s="1">
         <v>3</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(D60, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G60</f>
@@ -8253,24 +8253,24 @@
         <v>0.1</v>
       </c>
       <c r="AK60" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL60" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(D61, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G61</f>
@@ -8353,24 +8353,24 @@
         <v>0.1</v>
       </c>
       <c r="AK61" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL61" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D62" s="1">
         <v>5</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(D62, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G62</f>
@@ -8456,24 +8456,24 @@
         <v>0.1</v>
       </c>
       <c r="AK62" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL62" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D63" s="1">
         <v>6</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(D63, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G63</f>
@@ -8562,24 +8562,24 @@
         <v>0.1</v>
       </c>
       <c r="AK63" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL63" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D64" s="1">
         <v>7</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(D64, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G64</f>
@@ -8665,24 +8665,24 @@
         <v>0.1</v>
       </c>
       <c r="AK64" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL64" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D65" s="1">
         <v>8</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(D65, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G65</f>
@@ -8765,24 +8765,24 @@
         <v>0.2</v>
       </c>
       <c r="AK65" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AL65" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="AL65" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="66" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D66" s="1">
         <v>3</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(D66, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G66</f>
@@ -8868,21 +8868,21 @@
         <v>0.1</v>
       </c>
       <c r="AK66" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="67" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(D67, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G67</f>
@@ -8965,24 +8965,24 @@
         <v>0.1</v>
       </c>
       <c r="AK67" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AL67" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="AL67" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="68" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" s="1">
         <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(D68, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G68</f>
@@ -9071,24 +9071,24 @@
         <v>0.15</v>
       </c>
       <c r="AK68" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL68" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69" s="1">
         <v>6</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(D69, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G69</f>
@@ -9177,24 +9177,24 @@
         <v>0.15</v>
       </c>
       <c r="AK69" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL69" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="70" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D70" s="1">
         <v>7</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(D70, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G70</f>
@@ -9280,24 +9280,24 @@
         <v>0.1</v>
       </c>
       <c r="AK70" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL70" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D71" s="1">
         <v>8</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(D71, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G71</f>
@@ -9386,24 +9386,24 @@
         <v>0.15</v>
       </c>
       <c r="AK71" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL71" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="72" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D72" s="1">
         <v>7</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(D72, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G72</f>
@@ -9492,24 +9492,24 @@
         <v>0.1</v>
       </c>
       <c r="AK72" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AL72" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D73" s="1">
         <v>8</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(D73, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G73</f>
@@ -9592,24 +9592,24 @@
         <v>0.1</v>
       </c>
       <c r="AK73" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AL73" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D74" s="1">
         <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(D74, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G74</f>
@@ -9692,24 +9692,24 @@
         <v>0.1</v>
       </c>
       <c r="AK74" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL74" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="75" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D75" s="1">
         <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(D75, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G75</f>
@@ -9795,24 +9795,24 @@
         <v>0.1</v>
       </c>
       <c r="AK75" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL75" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="AL75" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="76" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D76" s="1">
         <v>2</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(D76, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G76</f>
@@ -9895,24 +9895,24 @@
         <v>0.1</v>
       </c>
       <c r="AK76" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="AL76" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="AL76" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="77" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D77" s="1">
         <v>3</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(D77, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G77</f>
@@ -9995,21 +9995,21 @@
         <v>0.1</v>
       </c>
       <c r="AK77" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D78" s="1">
         <v>4</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(D78, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G78</f>
@@ -10092,24 +10092,24 @@
         <v>0.1</v>
       </c>
       <c r="AK78" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL78" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D79" s="1">
         <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(D79, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G79</f>
@@ -10192,24 +10192,24 @@
         <v>0.1</v>
       </c>
       <c r="AK79" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL79" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D80" s="1">
         <v>6</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(D80, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G80</f>
@@ -10292,24 +10292,24 @@
         <v>0.1</v>
       </c>
       <c r="AK80" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL80" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D81" s="1">
         <v>7</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(D81, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G81</f>
@@ -10392,24 +10392,24 @@
         <v>0.1</v>
       </c>
       <c r="AK81" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL81" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="82" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D82" s="1">
         <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(D82, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G82</f>
@@ -10492,24 +10492,24 @@
         <v>0.2</v>
       </c>
       <c r="AK82" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL82" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D83" s="1">
         <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(D83, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G83</f>
@@ -10592,24 +10592,24 @@
         <v>0.2</v>
       </c>
       <c r="AK83" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL83" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="84" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D84" s="1">
         <v>8</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(D84, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G84</f>
@@ -10692,24 +10692,24 @@
         <v>0.2</v>
       </c>
       <c r="AK84" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL84" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="85" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D85" s="1">
         <v>8</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(D85, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G85</f>
@@ -10792,24 +10792,24 @@
         <v>0.2</v>
       </c>
       <c r="AK85" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL85" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="86" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D86" s="1">
         <v>2</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F86" s="1">
         <f>VLOOKUP(D86, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G86</f>
@@ -10892,24 +10892,24 @@
         <v>0.1</v>
       </c>
       <c r="AK86" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AL86" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F87" s="1">
         <f>VLOOKUP(D87, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G87</f>
@@ -10992,24 +10992,24 @@
         <v>0.15</v>
       </c>
       <c r="AK87" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AL87" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="88" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D88" s="1">
         <v>4</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F88" s="1">
         <f>VLOOKUP(D88, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G88</f>
@@ -11092,24 +11092,24 @@
         <v>0.15</v>
       </c>
       <c r="AK88" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="AL88" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="AL88" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="89" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D89" s="1">
         <v>5</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F89" s="1">
         <f>VLOOKUP(D89, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G89</f>
@@ -11192,24 +11192,24 @@
         <v>0.2</v>
       </c>
       <c r="AK89" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL89" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D90" s="1">
         <v>6</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F90" s="1">
         <f>VLOOKUP(D90, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G90</f>
@@ -11292,24 +11292,24 @@
         <v>0.2</v>
       </c>
       <c r="AK90" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="AL90" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="AL90" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="91" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D91" s="1">
         <v>7</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F91" s="1">
         <f>VLOOKUP(D91, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G91</f>
@@ -11392,24 +11392,24 @@
         <v>0.25</v>
       </c>
       <c r="AK91" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL91" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="92" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D92" s="1">
         <v>4</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F92" s="1">
         <f>VLOOKUP(D92, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G92</f>
@@ -11492,21 +11492,21 @@
         <v>0.05</v>
       </c>
       <c r="AK92" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="93" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D93" s="1">
         <v>6</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F93" s="1">
         <f>VLOOKUP(D93, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G93</f>
@@ -11589,24 +11589,24 @@
         <v>0.05</v>
       </c>
       <c r="AK93" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="AL93" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="AL93" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="94" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D94" s="1">
         <v>2</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F94" s="1">
         <f>VLOOKUP(D94, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G94</f>
@@ -11686,24 +11686,24 @@
         <v>0.1</v>
       </c>
       <c r="AK94" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AL94" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="AL94" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="95" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F95" s="1">
         <f>VLOOKUP(D95, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G95</f>
@@ -11786,24 +11786,24 @@
         <v>0.15</v>
       </c>
       <c r="AK95" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AL95" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D96" s="1">
         <v>4</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F96" s="1">
         <f>VLOOKUP(D96, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G96</f>
@@ -11883,24 +11883,24 @@
         <v>0.1</v>
       </c>
       <c r="AK96" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL96" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="97" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D97" s="1">
         <v>5</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F97" s="1">
         <f>VLOOKUP(D97, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G97</f>
@@ -11983,21 +11983,21 @@
         <v>0.1</v>
       </c>
       <c r="AK97" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D98" s="1">
         <v>6</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F98" s="1">
         <f>VLOOKUP(D98, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G98</f>
@@ -12080,24 +12080,24 @@
         <v>0.1</v>
       </c>
       <c r="AK98" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL98" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D99" s="1">
         <v>7</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F99" s="1">
         <f>VLOOKUP(D99, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G99</f>
@@ -12180,24 +12180,24 @@
         <v>0.15</v>
       </c>
       <c r="AK99" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AL99" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="100" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D100" s="1">
         <v>2</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F100" s="1">
         <f>VLOOKUP(D100, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G100</f>
@@ -12280,21 +12280,21 @@
         <v>0.05</v>
       </c>
       <c r="AK100" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D101" s="1">
         <v>3</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F101" s="1">
         <f>VLOOKUP(D101, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G101</f>
@@ -12377,24 +12377,24 @@
         <v>0.05</v>
       </c>
       <c r="AK101" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AL101" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D102" s="1">
         <v>4</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F102" s="1">
         <f>VLOOKUP(D102, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G102</f>
@@ -12477,24 +12477,24 @@
         <v>0.05</v>
       </c>
       <c r="AK102" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AL102" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D103" s="1">
         <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F103" s="1">
         <f>VLOOKUP(D103, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G103</f>
@@ -12577,24 +12577,24 @@
         <v>0.05</v>
       </c>
       <c r="AK103" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AL103" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D104" s="1">
         <v>6</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F104" s="1">
         <f>VLOOKUP(D104, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G104</f>
@@ -12677,24 +12677,24 @@
         <v>0.05</v>
       </c>
       <c r="AK104" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AL104" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D105" s="1">
         <v>7</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F105" s="1">
         <f>VLOOKUP(D105, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G105</f>
@@ -12777,24 +12777,24 @@
         <v>0.1</v>
       </c>
       <c r="AK105" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL105" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D106" s="1">
         <v>7</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F106" s="1">
         <f>VLOOKUP(D106, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G106</f>
@@ -12883,24 +12883,24 @@
         <v>0.2</v>
       </c>
       <c r="AK106" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL106" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D107" s="1">
         <v>8</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F107" s="1">
         <f>VLOOKUP(D107, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G107</f>
@@ -12983,24 +12983,24 @@
         <v>0.1</v>
       </c>
       <c r="AK107" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL107" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="AL107" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="108" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D108" s="1">
         <v>2</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F108" s="1">
         <f>VLOOKUP(D108, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G108</f>
@@ -13086,21 +13086,21 @@
         <v>0.05</v>
       </c>
       <c r="AK108" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="109" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F109" s="1">
         <f>VLOOKUP(D109, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G109</f>
@@ -13186,24 +13186,24 @@
         <v>0.05</v>
       </c>
       <c r="AK109" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AL109" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="AL109" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="110" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D110" s="1">
         <v>4</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F110" s="1">
         <f>VLOOKUP(D110, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G110</f>
@@ -13289,24 +13289,24 @@
         <v>0.05</v>
       </c>
       <c r="AK110" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AL110" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="AL110" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="111" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D111" s="1">
         <v>5</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F111" s="1">
         <f>VLOOKUP(D111, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G111</f>
@@ -13392,24 +13392,24 @@
         <v>0.05</v>
       </c>
       <c r="AK111" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL111" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="112" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D112" s="1">
         <v>2</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F112" s="1">
         <f>VLOOKUP(D112, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G112</f>
@@ -13495,21 +13495,21 @@
         <v>0.15</v>
       </c>
       <c r="AK112" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="113" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F113" s="1">
         <f>VLOOKUP(D113, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G113</f>
@@ -13595,21 +13595,21 @@
         <v>0.15</v>
       </c>
       <c r="AK113" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D114" s="1">
         <v>4</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F114" s="1">
         <f>VLOOKUP(D114, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G114</f>
@@ -13695,21 +13695,21 @@
         <v>0.2</v>
       </c>
       <c r="AK114" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D115" s="1">
         <v>5</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F115" s="1">
         <f>VLOOKUP(D115, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G115</f>
@@ -13795,21 +13795,21 @@
         <v>0.2</v>
       </c>
       <c r="AK115" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="116" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D116" s="1">
         <v>6</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F116" s="1">
         <f>VLOOKUP(D116, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G116</f>
@@ -13895,21 +13895,21 @@
         <v>0.25</v>
       </c>
       <c r="AK116" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="117" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D117" s="1">
         <v>7</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F117" s="1">
         <f>VLOOKUP(D117, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G117</f>
@@ -13995,21 +13995,21 @@
         <v>0.25</v>
       </c>
       <c r="AK117" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="118" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D118" s="1">
         <v>8</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F118" s="1">
         <f>VLOOKUP(D118, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G118</f>
@@ -14095,21 +14095,21 @@
         <v>0.25</v>
       </c>
       <c r="AK118" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="119" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D119" s="1">
         <v>9</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F119" s="1">
         <f>VLOOKUP(D119, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G119</f>
@@ -14195,21 +14195,21 @@
         <v>0.3</v>
       </c>
       <c r="AK119" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="120" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F120" s="1">
         <f>VLOOKUP(D120, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G120</f>
@@ -14289,24 +14289,24 @@
         <v>0.15</v>
       </c>
       <c r="AK120" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL120" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="121" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D121" s="1">
         <v>4</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F121" s="1">
         <f>VLOOKUP(D121, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G121</f>
@@ -14395,24 +14395,24 @@
         <v>0.05</v>
       </c>
       <c r="AK121" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL121" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="122" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D122" s="1">
         <v>5</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F122" s="1">
         <f>VLOOKUP(D122, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G122</f>
@@ -14495,24 +14495,24 @@
         <v>0.05</v>
       </c>
       <c r="AK122" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL122" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D123" s="1">
         <v>6</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F123" s="1">
         <f>VLOOKUP(D123, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G123</f>
@@ -14595,24 +14595,24 @@
         <v>0.1</v>
       </c>
       <c r="AK123" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL123" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D124" s="1">
         <v>7</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F124" s="1">
         <f>VLOOKUP(D124, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G124</f>
@@ -14695,24 +14695,24 @@
         <v>0.15</v>
       </c>
       <c r="AK124" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL124" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="125" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D125" s="1">
         <v>2</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F125" s="1">
         <f>VLOOKUP(D125, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G125</f>
@@ -14795,24 +14795,24 @@
         <v>0.05</v>
       </c>
       <c r="AK125" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL125" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="126" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F126" s="1">
         <f>VLOOKUP(D126, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G126</f>
@@ -14895,24 +14895,24 @@
         <v>0.15</v>
       </c>
       <c r="AK126" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL126" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D127" s="1">
         <v>4</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F127" s="1">
         <f>VLOOKUP(D127, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G127</f>
@@ -14995,21 +14995,21 @@
         <v>0.2</v>
       </c>
       <c r="AK127" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="128" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D128" s="1">
         <v>5</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F128" s="1">
         <f>VLOOKUP(D128, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G128</f>
@@ -15092,24 +15092,24 @@
         <v>0.2</v>
       </c>
       <c r="AK128" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="AL128" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="AL128" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="129" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D129" s="1">
         <v>6</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F129" s="1">
         <f>VLOOKUP(D129, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G129</f>
@@ -15183,24 +15183,24 @@
         <v>0.9</v>
       </c>
       <c r="AK129" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AL129" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="AL129" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="130" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D130" s="1">
         <v>3</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F130" s="1">
         <f>VLOOKUP(D130, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G130</f>
@@ -15283,24 +15283,24 @@
         <v>0.05</v>
       </c>
       <c r="AK130" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="AL130" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="AL130" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="131" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D131" s="1">
         <v>4</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F131" s="1">
         <f>VLOOKUP(D131, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G131</f>
@@ -15383,24 +15383,24 @@
         <v>0.05</v>
       </c>
       <c r="AK131" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="AL131" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="AL131" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="132" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D132" s="1">
         <v>5</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F132" s="1">
         <f>VLOOKUP(D132, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G132</f>
@@ -15483,24 +15483,24 @@
         <v>0.2</v>
       </c>
       <c r="AK132" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AL132" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="133" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D133" s="1">
         <v>2</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F133" s="1">
         <f>VLOOKUP(D133, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G133</f>
@@ -15574,21 +15574,21 @@
         <v>0.5</v>
       </c>
       <c r="AK133" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="134" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D134" s="1">
         <v>3</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F134" s="1">
         <f>VLOOKUP(D134, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G134</f>
@@ -15665,21 +15665,21 @@
         <v>0.05</v>
       </c>
       <c r="AK134" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="135" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D135" s="1">
         <v>4</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F135" s="1">
         <f>VLOOKUP(D135, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G135</f>
@@ -15756,24 +15756,24 @@
         <v>0.05</v>
       </c>
       <c r="AK135" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AL135" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="136" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D136" s="1">
         <v>5</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F136" s="1">
         <f>VLOOKUP(D136, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G136</f>
@@ -15850,24 +15850,24 @@
         <v>0.05</v>
       </c>
       <c r="AK136" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL136" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="137" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D137" s="1">
         <v>6</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F137" s="1">
         <f>VLOOKUP(D137, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G137</f>
@@ -15944,21 +15944,21 @@
         <v>0.05</v>
       </c>
       <c r="AK137" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="138" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D138" s="1">
         <v>7</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F138" s="1">
         <f>VLOOKUP(D138, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G138</f>
@@ -16044,24 +16044,24 @@
         <v>0.05</v>
       </c>
       <c r="AK138" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AL138" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="139" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D139" s="1">
         <v>3</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F139" s="1">
         <f>VLOOKUP(D139, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G139</f>
@@ -16144,24 +16144,24 @@
         <v>0.1</v>
       </c>
       <c r="AK139" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AL139" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D140" s="1">
         <v>6</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F140" s="1">
         <f>VLOOKUP(D140, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G140</f>
@@ -16247,24 +16247,24 @@
         <v>0.1</v>
       </c>
       <c r="AK140" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AL140" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="141" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D141" s="1">
         <v>1</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F141" s="1">
         <f>VLOOKUP(D141, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G141</f>
@@ -16347,21 +16347,21 @@
         <v>0.05</v>
       </c>
       <c r="AK141" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D142" s="1">
         <v>2</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F142" s="1">
         <f>VLOOKUP(D142, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G142</f>
@@ -16444,24 +16444,24 @@
         <v>0.1</v>
       </c>
       <c r="AK142" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL142" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="143" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D143" s="1">
         <v>3</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F143" s="1">
         <f>VLOOKUP(D143, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G143</f>
@@ -16544,24 +16544,24 @@
         <v>0.15</v>
       </c>
       <c r="AK143" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL143" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="144" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D144" s="1">
         <v>4</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F144" s="1">
         <f>VLOOKUP(D144, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G144</f>
@@ -16644,24 +16644,24 @@
         <v>0.1</v>
       </c>
       <c r="AK144" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="AL144" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="AL144" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="145" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D145" s="1">
         <v>9</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F145" s="1">
         <f>VLOOKUP(D145, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G145</f>
@@ -16744,36 +16744,36 @@
         <v>0.1</v>
       </c>
       <c r="AK145" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AL145" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AL145" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="AM145" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AN145" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="AN145" s="1" t="s">
+      <c r="AO145" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="AO145" s="1" t="s">
+      <c r="AP145" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="AP145" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="146" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D146" s="1">
         <v>9</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F146" s="1">
         <f>VLOOKUP(D146, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G146</f>
@@ -16856,36 +16856,36 @@
         <v>0.3</v>
       </c>
       <c r="AK146" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL146" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AM146" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="AN146" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="AO146" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="AN146" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="AO146" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="AP146" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="147" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D147" s="1">
         <v>9</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F147" s="1">
         <f>VLOOKUP(D147, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G147</f>
@@ -16971,45 +16971,45 @@
         <v>0.3</v>
       </c>
       <c r="AK147" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AL147" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AM147" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="AM147" s="1" t="s">
+      <c r="AN147" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="AN147" s="1" t="s">
+      <c r="AO147" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="AO147" s="1" t="s">
+      <c r="AP147" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="AP147" s="1" t="s">
+      <c r="AQ147" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="AQ147" s="1" t="s">
+      <c r="AR147" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AR147" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="AS147" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="148" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D148" s="1">
         <v>9</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F148" s="1">
         <f>VLOOKUP(D148, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G148</f>
@@ -17095,33 +17095,33 @@
         <v>0.3</v>
       </c>
       <c r="AK148" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AL148" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="AM148" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AM148" s="1" t="s">
+      <c r="AN148" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="AN148" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="AO148" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="149" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D149" s="1">
         <v>9</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F149" s="1">
         <f>VLOOKUP(D149, [1]Sheet1!$A$5:$L$14, 2, FALSE)*G149</f>
@@ -17204,22 +17204,22 @@
         <v>0.35</v>
       </c>
       <c r="AK149" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AL149" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="AM149" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AL149" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="AM149" s="1" t="s">
+      <c r="AN149" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="AN149" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="AO149" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AP149" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -17230,7 +17230,7 @@
     <mergeCell ref="AK1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A5:H34 Y5:XFD34 I5:X149 H6:H149 F35:H149 A5:A149 B6:B149">
+  <conditionalFormatting sqref="A5:H34 Y5:XFD34 A5:A149 I5:X149 B6:B149 H6:H149 F35:H149">
     <cfRule type="expression" priority="5">
       <formula xml:space="preserve"> MOD(ROW(),2)</formula>
     </cfRule>

--- a/design/MiniTemplate/Excels/#role.xlsx
+++ b/design/MiniTemplate/Excels/#role.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BiliBili\Work\slime\design\MiniTemplate\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3563CC-47BC-41A4-8F74-89DFC0480BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5868524A-AC03-45C7-816D-577D1A7E1A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1461,23 +1461,24 @@
     <t>h140</t>
   </si>
   <si>
-    <t>h141</t>
-  </si>
-  <si>
-    <t>h142</t>
-  </si>
-  <si>
-    <t>h143</t>
-  </si>
-  <si>
-    <t>h144</t>
-  </si>
-  <si>
-    <t>h145</t>
-  </si>
-  <si>
     <t>relations</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b2</t>
+  </si>
+  <si>
+    <t>b3</t>
+  </si>
+  <si>
+    <t>b4</t>
+  </si>
+  <si>
+    <t>b5</t>
   </si>
 </sst>
 </file>
@@ -2452,7 +2453,7 @@
         <v>186</v>
       </c>
       <c r="Y1" s="10" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="Z1" s="11"/>
       <c r="AA1" s="11"/>
@@ -16652,7 +16653,7 @@
     </row>
     <row r="145" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>181</v>
@@ -16764,7 +16765,7 @@
     </row>
     <row r="146" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>182</v>
@@ -16876,7 +16877,7 @@
     </row>
     <row r="147" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>183</v>
@@ -17000,7 +17001,7 @@
     </row>
     <row r="148" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>184</v>
@@ -17112,7 +17113,7 @@
     </row>
     <row r="149" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>185</v>
@@ -17230,7 +17231,7 @@
     <mergeCell ref="AK1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A5:H34 Y5:XFD34 A5:A149 I5:X149 B6:B149 H6:H149 F35:H149">
+  <conditionalFormatting sqref="A5:H34 Y5:XFD34 A5:A149 I5:X149 H6:H149 F35:H149 B6:B149">
     <cfRule type="expression" priority="5">
       <formula xml:space="preserve"> MOD(ROW(),2)</formula>
     </cfRule>
